--- a/Documentation/XML/Documentation_OfficialResults_3rdAmendment.xlsx
+++ b/Documentation/XML/Documentation_OfficialResults_3rdAmendment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QUAM\Workspace\VECTO_DEV_Buses\Documentation\XML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97719381-2618-4F3E-B84C-083331790E75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D89137A-A40D-4DA8-8584-8746C58668A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500" tabRatio="817" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <definedName name="_Hlk1133947" localSheetId="8">MRF_Content_perArchitecture!#REF!</definedName>
     <definedName name="Z_638E9BBB_9DE1_4C03_99E5_6DF442C45AE3_.wvu.FilterData" localSheetId="8" hidden="1">MRF_Content_perArchitecture!$A$1:$A$264</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <customWorkbookViews>
     <customWorkbookView name="Quaritsch Markus - Persönliche Ansicht" guid="{638E9BBB-9DE1-4C03-99E5-6DF442C45AE3}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="2576" windowHeight="1408" tabRatio="817" activeSheetId="9"/>
   </customWorkbookViews>
@@ -6710,11 +6710,17 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6733,9 +6739,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -6760,9 +6763,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7597,7 +7597,7 @@
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="C6" s="113"/>
+      <c r="C6" s="96"/>
       <c r="D6" t="s">
         <v>901</v>
       </c>
@@ -7682,156 +7682,156 @@
       <c r="C16" s="49"/>
     </row>
     <row r="17" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D17" s="97" t="s">
+      <c r="D17" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="96" t="s">
+      <c r="E17" s="98"/>
+      <c r="F17" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="J17" s="97" t="s">
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="J17" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="K17" s="97"/>
-      <c r="L17" s="96" t="s">
+      <c r="K17" s="98"/>
+      <c r="L17" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="P17" s="97" t="s">
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="P17" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="Q17" s="97"/>
-      <c r="R17" s="96" t="s">
+      <c r="Q17" s="98"/>
+      <c r="R17" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="V17" s="97" t="s">
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="V17" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="W17" s="97"/>
-      <c r="X17" s="96" t="s">
+      <c r="W17" s="98"/>
+      <c r="X17" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AB17" s="97" t="s">
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AB17" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="AC17" s="97"/>
-      <c r="AD17" s="96" t="s">
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="AE17" s="96"/>
-      <c r="AF17" s="96"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
     </row>
     <row r="18" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D18" s="98" t="s">
+      <c r="D18" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F18" s="100" t="s">
+      <c r="F18" s="102" t="s">
         <v>904</v>
       </c>
-      <c r="G18" s="101"/>
-      <c r="H18" s="102"/>
-      <c r="J18" s="98" t="s">
+      <c r="G18" s="103"/>
+      <c r="H18" s="104"/>
+      <c r="J18" s="100" t="s">
         <v>1</v>
       </c>
       <c r="K18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="L18" s="100" t="s">
+      <c r="L18" s="102" t="s">
         <v>904</v>
       </c>
-      <c r="M18" s="101"/>
-      <c r="N18" s="102"/>
-      <c r="P18" s="98" t="s">
+      <c r="M18" s="103"/>
+      <c r="N18" s="104"/>
+      <c r="P18" s="100" t="s">
         <v>1</v>
       </c>
       <c r="Q18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="R18" s="100" t="s">
+      <c r="R18" s="102" t="s">
         <v>904</v>
       </c>
-      <c r="S18" s="101"/>
-      <c r="T18" s="102"/>
-      <c r="V18" s="98" t="s">
+      <c r="S18" s="103"/>
+      <c r="T18" s="104"/>
+      <c r="V18" s="100" t="s">
         <v>1</v>
       </c>
       <c r="W18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="X18" s="100" t="s">
+      <c r="X18" s="102" t="s">
         <v>904</v>
       </c>
-      <c r="Y18" s="101"/>
-      <c r="Z18" s="102"/>
-      <c r="AB18" s="98" t="s">
+      <c r="Y18" s="103"/>
+      <c r="Z18" s="104"/>
+      <c r="AB18" s="100" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="AD18" s="100" t="s">
+      <c r="AD18" s="102" t="s">
         <v>904</v>
       </c>
-      <c r="AE18" s="101"/>
-      <c r="AF18" s="102"/>
+      <c r="AE18" s="103"/>
+      <c r="AF18" s="104"/>
     </row>
     <row r="19" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D19" s="99"/>
+      <c r="D19" s="101"/>
       <c r="E19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F19" s="103" t="s">
+      <c r="F19" s="105" t="s">
         <v>799</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
       <c r="I19" s="21"/>
-      <c r="J19" s="99"/>
+      <c r="J19" s="101"/>
       <c r="K19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="103" t="s">
+      <c r="L19" s="105" t="s">
         <v>799</v>
       </c>
-      <c r="M19" s="103"/>
-      <c r="N19" s="103"/>
-      <c r="P19" s="99"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="105"/>
+      <c r="P19" s="101"/>
       <c r="Q19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="R19" s="103" t="s">
+      <c r="R19" s="105" t="s">
         <v>799</v>
       </c>
-      <c r="S19" s="103"/>
-      <c r="T19" s="103"/>
-      <c r="V19" s="99"/>
+      <c r="S19" s="105"/>
+      <c r="T19" s="105"/>
+      <c r="V19" s="101"/>
       <c r="W19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X19" s="103" t="s">
+      <c r="X19" s="105" t="s">
         <v>799</v>
       </c>
-      <c r="Y19" s="103"/>
-      <c r="Z19" s="103"/>
-      <c r="AB19" s="99"/>
+      <c r="Y19" s="105"/>
+      <c r="Z19" s="105"/>
+      <c r="AB19" s="101"/>
       <c r="AC19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="AD19" s="103" t="s">
+      <c r="AD19" s="105" t="s">
         <v>799</v>
       </c>
-      <c r="AE19" s="103"/>
-      <c r="AF19" s="103"/>
+      <c r="AE19" s="105"/>
+      <c r="AF19" s="105"/>
     </row>
     <row r="20" spans="4:32" x14ac:dyDescent="0.25">
       <c r="D20" s="47" t="s">
@@ -7840,11 +7840,11 @@
       <c r="E20" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="F20" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
       <c r="I20" s="21"/>
       <c r="J20" s="47" t="s">
         <v>265</v>
@@ -7852,44 +7852,44 @@
       <c r="K20" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="L20" s="103" t="s">
+      <c r="L20" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="M20" s="103"/>
-      <c r="N20" s="103"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="105"/>
       <c r="P20" s="47" t="s">
         <v>265</v>
       </c>
       <c r="Q20" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="R20" s="103" t="s">
+      <c r="R20" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="S20" s="103"/>
-      <c r="T20" s="103"/>
+      <c r="S20" s="105"/>
+      <c r="T20" s="105"/>
       <c r="V20" s="86" t="s">
         <v>265</v>
       </c>
       <c r="W20" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="X20" s="103" t="s">
+      <c r="X20" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="Y20" s="103"/>
-      <c r="Z20" s="103"/>
+      <c r="Y20" s="105"/>
+      <c r="Z20" s="105"/>
       <c r="AB20" s="86" t="s">
         <v>265</v>
       </c>
       <c r="AC20" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="AD20" s="103" t="s">
+      <c r="AD20" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="AE20" s="103"/>
-      <c r="AF20" s="103"/>
+      <c r="AE20" s="105"/>
+      <c r="AF20" s="105"/>
     </row>
     <row r="21" spans="4:32" x14ac:dyDescent="0.25">
       <c r="D21" s="47" t="s">
@@ -7898,11 +7898,11 @@
       <c r="E21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F21" s="103" t="s">
+      <c r="F21" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
       <c r="I21" s="21"/>
       <c r="J21" s="47" t="s">
         <v>266</v>
@@ -7910,44 +7910,44 @@
       <c r="K21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="L21" s="103" t="s">
+      <c r="L21" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="M21" s="103"/>
-      <c r="N21" s="103"/>
+      <c r="M21" s="105"/>
+      <c r="N21" s="105"/>
       <c r="P21" s="47" t="s">
         <v>266</v>
       </c>
       <c r="Q21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="R21" s="103" t="s">
+      <c r="R21" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="S21" s="103"/>
-      <c r="T21" s="103"/>
+      <c r="S21" s="105"/>
+      <c r="T21" s="105"/>
       <c r="V21" s="86" t="s">
         <v>266</v>
       </c>
       <c r="W21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X21" s="103" t="s">
+      <c r="X21" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="Y21" s="103"/>
-      <c r="Z21" s="103"/>
+      <c r="Y21" s="105"/>
+      <c r="Z21" s="105"/>
       <c r="AB21" s="86" t="s">
         <v>266</v>
       </c>
       <c r="AC21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="AD21" s="103" t="s">
+      <c r="AD21" s="105" t="s">
         <v>800</v>
       </c>
-      <c r="AE21" s="103"/>
-      <c r="AF21" s="103"/>
+      <c r="AE21" s="105"/>
+      <c r="AF21" s="105"/>
     </row>
     <row r="22" spans="4:32" x14ac:dyDescent="0.25">
       <c r="D22" s="47" t="s">
@@ -7956,11 +7956,11 @@
       <c r="E22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F22" s="103" t="s">
+      <c r="F22" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
       <c r="I22" s="21"/>
       <c r="J22" s="47" t="s">
         <v>267</v>
@@ -7968,50 +7968,50 @@
       <c r="K22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="L22" s="103" t="s">
+      <c r="L22" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="103"/>
-      <c r="N22" s="103"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
       <c r="P22" s="47" t="s">
         <v>267</v>
       </c>
       <c r="Q22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="R22" s="103" t="s">
+      <c r="R22" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="S22" s="103"/>
-      <c r="T22" s="103"/>
+      <c r="S22" s="105"/>
+      <c r="T22" s="105"/>
       <c r="V22" s="86" t="s">
         <v>267</v>
       </c>
       <c r="W22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X22" s="103" t="s">
+      <c r="X22" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="Y22" s="103"/>
-      <c r="Z22" s="103"/>
+      <c r="Y22" s="105"/>
+      <c r="Z22" s="105"/>
       <c r="AB22" s="86" t="s">
         <v>267</v>
       </c>
       <c r="AC22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="AD22" s="103" t="s">
+      <c r="AD22" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AE22" s="103"/>
-      <c r="AF22" s="103"/>
+      <c r="AE22" s="105"/>
+      <c r="AF22" s="105"/>
     </row>
     <row r="23" spans="4:32" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="104"/>
+      <c r="E23" s="97"/>
       <c r="F23" s="50" t="s">
         <v>305</v>
       </c>
@@ -8022,10 +8022,10 @@
         <v>10</v>
       </c>
       <c r="I23" s="21"/>
-      <c r="J23" s="104" t="s">
+      <c r="J23" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="K23" s="104"/>
+      <c r="K23" s="97"/>
       <c r="L23" s="50" t="s">
         <v>305</v>
       </c>
@@ -8035,10 +8035,10 @@
       <c r="N23" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="P23" s="104" t="s">
+      <c r="P23" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="Q23" s="104"/>
+      <c r="Q23" s="97"/>
       <c r="R23" s="50" t="s">
         <v>305</v>
       </c>
@@ -8048,10 +8048,10 @@
       <c r="T23" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="V23" s="104" t="s">
+      <c r="V23" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="W23" s="104"/>
+      <c r="W23" s="97"/>
       <c r="X23" s="50" t="s">
         <v>305</v>
       </c>
@@ -8061,10 +8061,10 @@
       <c r="Z23" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="AB23" s="104" t="s">
+      <c r="AB23" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="AC23" s="104"/>
+      <c r="AC23" s="97"/>
       <c r="AD23" s="50" t="s">
         <v>305</v>
       </c>
@@ -8154,7 +8154,7 @@
       </c>
     </row>
     <row r="25" spans="4:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="104" t="s">
+      <c r="D25" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E25" s="42" t="s">
@@ -8170,7 +8170,7 @@
         <v>11</v>
       </c>
       <c r="I25" s="21"/>
-      <c r="J25" s="104" t="s">
+      <c r="J25" s="97" t="s">
         <v>269</v>
       </c>
       <c r="K25" s="42" t="s">
@@ -8185,7 +8185,7 @@
       <c r="N25" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P25" s="104" t="s">
+      <c r="P25" s="97" t="s">
         <v>269</v>
       </c>
       <c r="Q25" s="42" t="s">
@@ -8200,7 +8200,7 @@
       <c r="T25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V25" s="104" t="s">
+      <c r="V25" s="97" t="s">
         <v>269</v>
       </c>
       <c r="W25" s="42" t="s">
@@ -8215,7 +8215,7 @@
       <c r="Z25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB25" s="104" t="s">
+      <c r="AB25" s="97" t="s">
         <v>269</v>
       </c>
       <c r="AC25" s="42" t="s">
@@ -8232,7 +8232,7 @@
       </c>
     </row>
     <row r="26" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>274</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>799</v>
       </c>
       <c r="I26" s="21"/>
-      <c r="J26" s="104"/>
+      <c r="J26" s="97"/>
       <c r="K26" s="42" t="s">
         <v>274</v>
       </c>
@@ -8259,7 +8259,7 @@
       <c r="N26" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P26" s="104"/>
+      <c r="P26" s="97"/>
       <c r="Q26" s="42" t="s">
         <v>274</v>
       </c>
@@ -8272,7 +8272,7 @@
       <c r="T26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V26" s="104"/>
+      <c r="V26" s="97"/>
       <c r="W26" s="42" t="s">
         <v>274</v>
       </c>
@@ -8285,7 +8285,7 @@
       <c r="Z26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB26" s="104"/>
+      <c r="AB26" s="97"/>
       <c r="AC26" s="42" t="s">
         <v>274</v>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
     </row>
     <row r="27" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>282</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>800</v>
       </c>
       <c r="I27" s="21"/>
-      <c r="J27" s="104"/>
+      <c r="J27" s="97"/>
       <c r="K27" s="42" t="s">
         <v>282</v>
       </c>
@@ -8327,7 +8327,7 @@
       <c r="N27" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P27" s="104"/>
+      <c r="P27" s="97"/>
       <c r="Q27" s="42" t="s">
         <v>282</v>
       </c>
@@ -8340,7 +8340,7 @@
       <c r="T27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V27" s="104"/>
+      <c r="V27" s="97"/>
       <c r="W27" s="42" t="s">
         <v>282</v>
       </c>
@@ -8353,7 +8353,7 @@
       <c r="Z27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB27" s="104"/>
+      <c r="AB27" s="97"/>
       <c r="AC27" s="42" t="s">
         <v>282</v>
       </c>
@@ -8368,7 +8368,7 @@
       </c>
     </row>
     <row r="28" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>275</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>799</v>
       </c>
       <c r="I28" s="36"/>
-      <c r="J28" s="104"/>
+      <c r="J28" s="97"/>
       <c r="K28" s="42" t="s">
         <v>275</v>
       </c>
@@ -8395,7 +8395,7 @@
       <c r="N28" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P28" s="104"/>
+      <c r="P28" s="97"/>
       <c r="Q28" s="42" t="s">
         <v>275</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="T28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V28" s="104"/>
+      <c r="V28" s="97"/>
       <c r="W28" s="42" t="s">
         <v>275</v>
       </c>
@@ -8421,7 +8421,7 @@
       <c r="Z28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB28" s="104"/>
+      <c r="AB28" s="97"/>
       <c r="AC28" s="42" t="s">
         <v>275</v>
       </c>
@@ -8436,7 +8436,7 @@
       </c>
     </row>
     <row r="29" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>302</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>11</v>
       </c>
       <c r="I29" s="33"/>
-      <c r="J29" s="104"/>
+      <c r="J29" s="97"/>
       <c r="K29" s="42" t="s">
         <v>302</v>
       </c>
@@ -8463,7 +8463,7 @@
       <c r="N29" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P29" s="104"/>
+      <c r="P29" s="97"/>
       <c r="Q29" s="42" t="s">
         <v>302</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="T29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V29" s="104"/>
+      <c r="V29" s="97"/>
       <c r="W29" s="42" t="s">
         <v>302</v>
       </c>
@@ -8489,7 +8489,7 @@
       <c r="Z29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB29" s="104"/>
+      <c r="AB29" s="97"/>
       <c r="AC29" s="42" t="s">
         <v>302</v>
       </c>
@@ -8504,7 +8504,7 @@
       </c>
     </row>
     <row r="30" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>284</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>799</v>
       </c>
       <c r="I30" s="33"/>
-      <c r="J30" s="104"/>
+      <c r="J30" s="97"/>
       <c r="K30" s="42" t="s">
         <v>284</v>
       </c>
@@ -8531,7 +8531,7 @@
       <c r="N30" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P30" s="104"/>
+      <c r="P30" s="97"/>
       <c r="Q30" s="42" t="s">
         <v>284</v>
       </c>
@@ -8544,7 +8544,7 @@
       <c r="T30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V30" s="104"/>
+      <c r="V30" s="97"/>
       <c r="W30" s="42" t="s">
         <v>284</v>
       </c>
@@ -8557,7 +8557,7 @@
       <c r="Z30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="104"/>
+      <c r="AB30" s="97"/>
       <c r="AC30" s="42" t="s">
         <v>284</v>
       </c>
@@ -8572,7 +8572,7 @@
       </c>
     </row>
     <row r="31" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>285</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>800</v>
       </c>
       <c r="I31" s="33"/>
-      <c r="J31" s="104"/>
+      <c r="J31" s="97"/>
       <c r="K31" s="42" t="s">
         <v>285</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="N31" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P31" s="104"/>
+      <c r="P31" s="97"/>
       <c r="Q31" s="42" t="s">
         <v>285</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="T31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V31" s="104"/>
+      <c r="V31" s="97"/>
       <c r="W31" s="42" t="s">
         <v>285</v>
       </c>
@@ -8625,7 +8625,7 @@
       <c r="Z31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB31" s="104"/>
+      <c r="AB31" s="97"/>
       <c r="AC31" s="42" t="s">
         <v>285</v>
       </c>
@@ -8640,7 +8640,7 @@
       </c>
     </row>
     <row r="32" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>286</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>799</v>
       </c>
       <c r="I32" s="33"/>
-      <c r="J32" s="104"/>
+      <c r="J32" s="97"/>
       <c r="K32" s="42" t="s">
         <v>286</v>
       </c>
@@ -8667,7 +8667,7 @@
       <c r="N32" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P32" s="104"/>
+      <c r="P32" s="97"/>
       <c r="Q32" s="42" t="s">
         <v>286</v>
       </c>
@@ -8680,7 +8680,7 @@
       <c r="T32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V32" s="104"/>
+      <c r="V32" s="97"/>
       <c r="W32" s="42" t="s">
         <v>286</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="Z32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB32" s="104"/>
+      <c r="AB32" s="97"/>
       <c r="AC32" s="42" t="s">
         <v>286</v>
       </c>
@@ -8708,7 +8708,7 @@
       </c>
     </row>
     <row r="33" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>276</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>11</v>
       </c>
       <c r="I33" s="33"/>
-      <c r="J33" s="104"/>
+      <c r="J33" s="97"/>
       <c r="K33" s="42" t="s">
         <v>276</v>
       </c>
@@ -8735,7 +8735,7 @@
       <c r="N33" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P33" s="104"/>
+      <c r="P33" s="97"/>
       <c r="Q33" s="42" t="s">
         <v>276</v>
       </c>
@@ -8748,7 +8748,7 @@
       <c r="T33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V33" s="104"/>
+      <c r="V33" s="97"/>
       <c r="W33" s="42" t="s">
         <v>276</v>
       </c>
@@ -8761,7 +8761,7 @@
       <c r="Z33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB33" s="104"/>
+      <c r="AB33" s="97"/>
       <c r="AC33" s="42" t="s">
         <v>276</v>
       </c>
@@ -8776,7 +8776,7 @@
       </c>
     </row>
     <row r="34" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>277</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>799</v>
       </c>
       <c r="I34" s="33"/>
-      <c r="J34" s="104"/>
+      <c r="J34" s="97"/>
       <c r="K34" s="42" t="s">
         <v>277</v>
       </c>
@@ -8803,7 +8803,7 @@
       <c r="N34" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P34" s="104"/>
+      <c r="P34" s="97"/>
       <c r="Q34" s="42" t="s">
         <v>277</v>
       </c>
@@ -8816,7 +8816,7 @@
       <c r="T34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V34" s="104"/>
+      <c r="V34" s="97"/>
       <c r="W34" s="42" t="s">
         <v>277</v>
       </c>
@@ -8829,7 +8829,7 @@
       <c r="Z34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB34" s="104"/>
+      <c r="AB34" s="97"/>
       <c r="AC34" s="42" t="s">
         <v>277</v>
       </c>
@@ -8844,7 +8844,7 @@
       </c>
     </row>
     <row r="35" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D35" s="104"/>
+      <c r="D35" s="97"/>
       <c r="E35" s="42" t="s">
         <v>283</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>800</v>
       </c>
       <c r="I35" s="33"/>
-      <c r="J35" s="104"/>
+      <c r="J35" s="97"/>
       <c r="K35" s="42" t="s">
         <v>283</v>
       </c>
@@ -8871,7 +8871,7 @@
       <c r="N35" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P35" s="104"/>
+      <c r="P35" s="97"/>
       <c r="Q35" s="42" t="s">
         <v>283</v>
       </c>
@@ -8884,7 +8884,7 @@
       <c r="T35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V35" s="104"/>
+      <c r="V35" s="97"/>
       <c r="W35" s="42" t="s">
         <v>283</v>
       </c>
@@ -8897,7 +8897,7 @@
       <c r="Z35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB35" s="104"/>
+      <c r="AB35" s="97"/>
       <c r="AC35" s="42" t="s">
         <v>283</v>
       </c>
@@ -8912,7 +8912,7 @@
       </c>
     </row>
     <row r="36" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D36" s="104"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="42" t="s">
         <v>278</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>799</v>
       </c>
       <c r="I36" s="33"/>
-      <c r="J36" s="104"/>
+      <c r="J36" s="97"/>
       <c r="K36" s="42" t="s">
         <v>278</v>
       </c>
@@ -8939,7 +8939,7 @@
       <c r="N36" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P36" s="104"/>
+      <c r="P36" s="97"/>
       <c r="Q36" s="42" t="s">
         <v>278</v>
       </c>
@@ -8952,7 +8952,7 @@
       <c r="T36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V36" s="104"/>
+      <c r="V36" s="97"/>
       <c r="W36" s="42" t="s">
         <v>278</v>
       </c>
@@ -8965,7 +8965,7 @@
       <c r="Z36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB36" s="104"/>
+      <c r="AB36" s="97"/>
       <c r="AC36" s="42" t="s">
         <v>278</v>
       </c>
@@ -8980,7 +8980,7 @@
       </c>
     </row>
     <row r="37" spans="4:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="104" t="s">
+      <c r="D37" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="42" t="s">
@@ -8996,7 +8996,7 @@
         <v>9</v>
       </c>
       <c r="I37" s="33"/>
-      <c r="J37" s="104" t="s">
+      <c r="J37" s="97" t="s">
         <v>4</v>
       </c>
       <c r="K37" s="42" t="s">
@@ -9011,7 +9011,7 @@
       <c r="N37" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P37" s="104" t="s">
+      <c r="P37" s="97" t="s">
         <v>4</v>
       </c>
       <c r="Q37" s="42" t="s">
@@ -9026,7 +9026,7 @@
       <c r="T37" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="V37" s="104" t="s">
+      <c r="V37" s="97" t="s">
         <v>4</v>
       </c>
       <c r="W37" s="42" t="s">
@@ -9041,7 +9041,7 @@
       <c r="Z37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB37" s="104" t="s">
+      <c r="AB37" s="97" t="s">
         <v>4</v>
       </c>
       <c r="AC37" s="42" t="s">
@@ -9058,7 +9058,7 @@
       </c>
     </row>
     <row r="38" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>280</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>9</v>
       </c>
       <c r="I38" s="38"/>
-      <c r="J38" s="104"/>
+      <c r="J38" s="97"/>
       <c r="K38" s="42" t="s">
         <v>280</v>
       </c>
@@ -9085,7 +9085,7 @@
       <c r="N38" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P38" s="104"/>
+      <c r="P38" s="97"/>
       <c r="Q38" s="42" t="s">
         <v>280</v>
       </c>
@@ -9098,7 +9098,7 @@
       <c r="T38" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V38" s="104"/>
+      <c r="V38" s="97"/>
       <c r="W38" s="42" t="s">
         <v>280</v>
       </c>
@@ -9111,7 +9111,7 @@
       <c r="Z38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB38" s="104"/>
+      <c r="AB38" s="97"/>
       <c r="AC38" s="42" t="s">
         <v>280</v>
       </c>
@@ -9126,7 +9126,7 @@
       </c>
     </row>
     <row r="39" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>287</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>9</v>
       </c>
       <c r="I39" s="38"/>
-      <c r="J39" s="104"/>
+      <c r="J39" s="97"/>
       <c r="K39" s="42" t="s">
         <v>287</v>
       </c>
@@ -9153,7 +9153,7 @@
       <c r="N39" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P39" s="104"/>
+      <c r="P39" s="97"/>
       <c r="Q39" s="42" t="s">
         <v>287</v>
       </c>
@@ -9166,7 +9166,7 @@
       <c r="T39" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V39" s="104"/>
+      <c r="V39" s="97"/>
       <c r="W39" s="42" t="s">
         <v>287</v>
       </c>
@@ -9179,7 +9179,7 @@
       <c r="Z39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB39" s="104"/>
+      <c r="AB39" s="97"/>
       <c r="AC39" s="42" t="s">
         <v>287</v>
       </c>
@@ -9194,7 +9194,7 @@
       </c>
     </row>
     <row r="40" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>281</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>9</v>
       </c>
       <c r="I40" s="38"/>
-      <c r="J40" s="104"/>
+      <c r="J40" s="97"/>
       <c r="K40" s="42" t="s">
         <v>281</v>
       </c>
@@ -9221,7 +9221,7 @@
       <c r="N40" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P40" s="104"/>
+      <c r="P40" s="97"/>
       <c r="Q40" s="42" t="s">
         <v>281</v>
       </c>
@@ -9234,7 +9234,7 @@
       <c r="T40" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V40" s="104"/>
+      <c r="V40" s="97"/>
       <c r="W40" s="42" t="s">
         <v>281</v>
       </c>
@@ -9247,7 +9247,7 @@
       <c r="Z40" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB40" s="104"/>
+      <c r="AB40" s="97"/>
       <c r="AC40" s="42" t="s">
         <v>281</v>
       </c>
@@ -9262,7 +9262,7 @@
       </c>
     </row>
     <row r="41" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>276</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>9</v>
       </c>
       <c r="I41" s="38"/>
-      <c r="J41" s="104"/>
+      <c r="J41" s="97"/>
       <c r="K41" s="42" t="s">
         <v>276</v>
       </c>
@@ -9289,7 +9289,7 @@
       <c r="N41" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P41" s="104"/>
+      <c r="P41" s="97"/>
       <c r="Q41" s="42" t="s">
         <v>276</v>
       </c>
@@ -9302,7 +9302,7 @@
       <c r="T41" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="V41" s="104"/>
+      <c r="V41" s="97"/>
       <c r="W41" s="42" t="s">
         <v>276</v>
       </c>
@@ -9315,7 +9315,7 @@
       <c r="Z41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB41" s="104"/>
+      <c r="AB41" s="97"/>
       <c r="AC41" s="42" t="s">
         <v>276</v>
       </c>
@@ -9330,7 +9330,7 @@
       </c>
     </row>
     <row r="42" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>277</v>
       </c>
@@ -9344,7 +9344,7 @@
         <v>9</v>
       </c>
       <c r="I42" s="38"/>
-      <c r="J42" s="104"/>
+      <c r="J42" s="97"/>
       <c r="K42" s="42" t="s">
         <v>277</v>
       </c>
@@ -9357,7 +9357,7 @@
       <c r="N42" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P42" s="104"/>
+      <c r="P42" s="97"/>
       <c r="Q42" s="42" t="s">
         <v>277</v>
       </c>
@@ -9370,7 +9370,7 @@
       <c r="T42" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V42" s="104"/>
+      <c r="V42" s="97"/>
       <c r="W42" s="42" t="s">
         <v>277</v>
       </c>
@@ -9383,7 +9383,7 @@
       <c r="Z42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB42" s="104"/>
+      <c r="AB42" s="97"/>
       <c r="AC42" s="42" t="s">
         <v>277</v>
       </c>
@@ -9398,7 +9398,7 @@
       </c>
     </row>
     <row r="43" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D43" s="104"/>
+      <c r="D43" s="97"/>
       <c r="E43" s="42" t="s">
         <v>283</v>
       </c>
@@ -9411,7 +9411,7 @@
       <c r="H43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J43" s="104"/>
+      <c r="J43" s="97"/>
       <c r="K43" s="42" t="s">
         <v>283</v>
       </c>
@@ -9424,7 +9424,7 @@
       <c r="N43" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P43" s="104"/>
+      <c r="P43" s="97"/>
       <c r="Q43" s="42" t="s">
         <v>283</v>
       </c>
@@ -9437,7 +9437,7 @@
       <c r="T43" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V43" s="104"/>
+      <c r="V43" s="97"/>
       <c r="W43" s="42" t="s">
         <v>283</v>
       </c>
@@ -9450,7 +9450,7 @@
       <c r="Z43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB43" s="104"/>
+      <c r="AB43" s="97"/>
       <c r="AC43" s="42" t="s">
         <v>283</v>
       </c>
@@ -9465,7 +9465,7 @@
       </c>
     </row>
     <row r="44" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D44" s="104"/>
+      <c r="D44" s="97"/>
       <c r="E44" s="42" t="s">
         <v>278</v>
       </c>
@@ -9478,7 +9478,7 @@
       <c r="H44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J44" s="104"/>
+      <c r="J44" s="97"/>
       <c r="K44" s="42" t="s">
         <v>278</v>
       </c>
@@ -9491,7 +9491,7 @@
       <c r="N44" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P44" s="104"/>
+      <c r="P44" s="97"/>
       <c r="Q44" s="42" t="s">
         <v>278</v>
       </c>
@@ -9504,7 +9504,7 @@
       <c r="T44" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V44" s="104"/>
+      <c r="V44" s="97"/>
       <c r="W44" s="42" t="s">
         <v>278</v>
       </c>
@@ -9517,7 +9517,7 @@
       <c r="Z44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB44" s="104"/>
+      <c r="AB44" s="97"/>
       <c r="AC44" s="42" t="s">
         <v>278</v>
       </c>
@@ -9532,7 +9532,7 @@
       </c>
     </row>
     <row r="45" spans="4:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="104" t="s">
+      <c r="D45" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="42" t="s">
@@ -9547,7 +9547,7 @@
       <c r="H45" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="J45" s="104" t="s">
+      <c r="J45" s="97" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="42" t="s">
@@ -9562,7 +9562,7 @@
       <c r="N45" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P45" s="104" t="s">
+      <c r="P45" s="97" t="s">
         <v>3</v>
       </c>
       <c r="Q45" s="42" t="s">
@@ -9577,7 +9577,7 @@
       <c r="T45" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V45" s="104" t="s">
+      <c r="V45" s="97" t="s">
         <v>3</v>
       </c>
       <c r="W45" s="42" t="s">
@@ -9592,7 +9592,7 @@
       <c r="Z45" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB45" s="104" t="s">
+      <c r="AB45" s="97" t="s">
         <v>3</v>
       </c>
       <c r="AC45" s="42" t="s">
@@ -9609,7 +9609,7 @@
       </c>
     </row>
     <row r="46" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>274</v>
       </c>
@@ -9622,7 +9622,7 @@
       <c r="H46" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J46" s="104"/>
+      <c r="J46" s="97"/>
       <c r="K46" s="42" t="s">
         <v>274</v>
       </c>
@@ -9635,7 +9635,7 @@
       <c r="N46" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P46" s="104"/>
+      <c r="P46" s="97"/>
       <c r="Q46" s="42" t="s">
         <v>274</v>
       </c>
@@ -9648,7 +9648,7 @@
       <c r="T46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V46" s="104"/>
+      <c r="V46" s="97"/>
       <c r="W46" s="42" t="s">
         <v>274</v>
       </c>
@@ -9661,7 +9661,7 @@
       <c r="Z46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB46" s="104"/>
+      <c r="AB46" s="97"/>
       <c r="AC46" s="42" t="s">
         <v>274</v>
       </c>
@@ -9676,7 +9676,7 @@
       </c>
     </row>
     <row r="47" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D47" s="104"/>
+      <c r="D47" s="97"/>
       <c r="E47" s="42" t="s">
         <v>282</v>
       </c>
@@ -9689,7 +9689,7 @@
       <c r="H47" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="J47" s="104"/>
+      <c r="J47" s="97"/>
       <c r="K47" s="42" t="s">
         <v>282</v>
       </c>
@@ -9702,7 +9702,7 @@
       <c r="N47" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P47" s="104"/>
+      <c r="P47" s="97"/>
       <c r="Q47" s="42" t="s">
         <v>282</v>
       </c>
@@ -9715,7 +9715,7 @@
       <c r="T47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V47" s="104"/>
+      <c r="V47" s="97"/>
       <c r="W47" s="42" t="s">
         <v>282</v>
       </c>
@@ -9728,7 +9728,7 @@
       <c r="Z47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB47" s="104"/>
+      <c r="AB47" s="97"/>
       <c r="AC47" s="42" t="s">
         <v>282</v>
       </c>
@@ -9743,7 +9743,7 @@
       </c>
     </row>
     <row r="48" spans="4:32" x14ac:dyDescent="0.25">
-      <c r="D48" s="104"/>
+      <c r="D48" s="97"/>
       <c r="E48" s="42" t="s">
         <v>275</v>
       </c>
@@ -9756,7 +9756,7 @@
       <c r="H48" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J48" s="104"/>
+      <c r="J48" s="97"/>
       <c r="K48" s="42" t="s">
         <v>275</v>
       </c>
@@ -9769,7 +9769,7 @@
       <c r="N48" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P48" s="104"/>
+      <c r="P48" s="97"/>
       <c r="Q48" s="42" t="s">
         <v>275</v>
       </c>
@@ -9782,7 +9782,7 @@
       <c r="T48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V48" s="104"/>
+      <c r="V48" s="97"/>
       <c r="W48" s="42" t="s">
         <v>275</v>
       </c>
@@ -9795,7 +9795,7 @@
       <c r="Z48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB48" s="104"/>
+      <c r="AB48" s="97"/>
       <c r="AC48" s="42" t="s">
         <v>275</v>
       </c>
@@ -9976,7 +9976,7 @@
       <c r="G51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="113" t="s">
+      <c r="H51" s="96" t="s">
         <v>11</v>
       </c>
       <c r="J51" s="48" t="s">
@@ -10053,7 +10053,7 @@
       <c r="G52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H52" s="113" t="s">
+      <c r="H52" s="96" t="s">
         <v>11</v>
       </c>
       <c r="J52" s="48" t="s">
@@ -10068,7 +10068,7 @@
       <c r="M52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N52" s="113" t="s">
+      <c r="N52" s="96" t="s">
         <v>11</v>
       </c>
       <c r="P52" s="48" t="s">
@@ -10195,7 +10195,7 @@
       </c>
     </row>
     <row r="54" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="104" t="s">
+      <c r="D54" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E54" s="43" t="s">
@@ -10207,10 +10207,10 @@
       <c r="G54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="113" t="s">
+      <c r="H54" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J54" s="104" t="s">
+      <c r="J54" s="97" t="s">
         <v>300</v>
       </c>
       <c r="K54" s="43" t="s">
@@ -10222,10 +10222,10 @@
       <c r="M54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N54" s="113" t="s">
+      <c r="N54" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P54" s="104" t="s">
+      <c r="P54" s="97" t="s">
         <v>300</v>
       </c>
       <c r="Q54" s="43" t="s">
@@ -10240,7 +10240,7 @@
       <c r="T54" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V54" s="104" t="s">
+      <c r="V54" s="97" t="s">
         <v>300</v>
       </c>
       <c r="W54" s="43" t="s">
@@ -10255,7 +10255,7 @@
       <c r="Z54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB54" s="104" t="s">
+      <c r="AB54" s="97" t="s">
         <v>300</v>
       </c>
       <c r="AC54" s="43" t="s">
@@ -10272,7 +10272,7 @@
       </c>
     </row>
     <row r="55" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>282</v>
       </c>
@@ -10282,10 +10282,10 @@
       <c r="G55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H55" s="113" t="s">
+      <c r="H55" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J55" s="104"/>
+      <c r="J55" s="97"/>
       <c r="K55" s="43" t="s">
         <v>282</v>
       </c>
@@ -10295,10 +10295,10 @@
       <c r="M55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N55" s="113" t="s">
+      <c r="N55" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P55" s="104"/>
+      <c r="P55" s="97"/>
       <c r="Q55" s="43" t="s">
         <v>282</v>
       </c>
@@ -10311,7 +10311,7 @@
       <c r="T55" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V55" s="104"/>
+      <c r="V55" s="97"/>
       <c r="W55" s="43" t="s">
         <v>282</v>
       </c>
@@ -10324,7 +10324,7 @@
       <c r="Z55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB55" s="104"/>
+      <c r="AB55" s="97"/>
       <c r="AC55" s="43" t="s">
         <v>282</v>
       </c>
@@ -10339,7 +10339,7 @@
       </c>
     </row>
     <row r="56" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>302</v>
       </c>
@@ -10349,10 +10349,10 @@
       <c r="G56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H56" s="113" t="s">
+      <c r="H56" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J56" s="104"/>
+      <c r="J56" s="97"/>
       <c r="K56" s="43" t="s">
         <v>302</v>
       </c>
@@ -10362,10 +10362,10 @@
       <c r="M56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N56" s="113" t="s">
+      <c r="N56" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P56" s="104"/>
+      <c r="P56" s="97"/>
       <c r="Q56" s="43" t="s">
         <v>302</v>
       </c>
@@ -10378,7 +10378,7 @@
       <c r="T56" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V56" s="104"/>
+      <c r="V56" s="97"/>
       <c r="W56" s="43" t="s">
         <v>302</v>
       </c>
@@ -10391,7 +10391,7 @@
       <c r="Z56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB56" s="104"/>
+      <c r="AB56" s="97"/>
       <c r="AC56" s="43" t="s">
         <v>302</v>
       </c>
@@ -10406,7 +10406,7 @@
       </c>
     </row>
     <row r="57" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D57" s="104"/>
+      <c r="D57" s="97"/>
       <c r="E57" s="43" t="s">
         <v>285</v>
       </c>
@@ -10416,10 +10416,10 @@
       <c r="G57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H57" s="113" t="s">
+      <c r="H57" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J57" s="104"/>
+      <c r="J57" s="97"/>
       <c r="K57" s="43" t="s">
         <v>285</v>
       </c>
@@ -10429,10 +10429,10 @@
       <c r="M57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N57" s="113" t="s">
+      <c r="N57" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P57" s="104"/>
+      <c r="P57" s="97"/>
       <c r="Q57" s="43" t="s">
         <v>285</v>
       </c>
@@ -10445,7 +10445,7 @@
       <c r="T57" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V57" s="104"/>
+      <c r="V57" s="97"/>
       <c r="W57" s="43" t="s">
         <v>285</v>
       </c>
@@ -10458,7 +10458,7 @@
       <c r="Z57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB57" s="104"/>
+      <c r="AB57" s="97"/>
       <c r="AC57" s="43" t="s">
         <v>285</v>
       </c>
@@ -10473,7 +10473,7 @@
       </c>
     </row>
     <row r="58" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D58" s="104"/>
+      <c r="D58" s="97"/>
       <c r="E58" s="43" t="s">
         <v>276</v>
       </c>
@@ -10483,10 +10483,10 @@
       <c r="G58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H58" s="113" t="s">
+      <c r="H58" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J58" s="104"/>
+      <c r="J58" s="97"/>
       <c r="K58" s="43" t="s">
         <v>276</v>
       </c>
@@ -10496,10 +10496,10 @@
       <c r="M58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N58" s="113" t="s">
+      <c r="N58" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P58" s="104"/>
+      <c r="P58" s="97"/>
       <c r="Q58" s="43" t="s">
         <v>276</v>
       </c>
@@ -10512,7 +10512,7 @@
       <c r="T58" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V58" s="104"/>
+      <c r="V58" s="97"/>
       <c r="W58" s="43" t="s">
         <v>276</v>
       </c>
@@ -10525,7 +10525,7 @@
       <c r="Z58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB58" s="104"/>
+      <c r="AB58" s="97"/>
       <c r="AC58" s="43" t="s">
         <v>276</v>
       </c>
@@ -10540,7 +10540,7 @@
       </c>
     </row>
     <row r="59" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D59" s="104"/>
+      <c r="D59" s="97"/>
       <c r="E59" s="43" t="s">
         <v>283</v>
       </c>
@@ -10550,10 +10550,10 @@
       <c r="G59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H59" s="113" t="s">
+      <c r="H59" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J59" s="104"/>
+      <c r="J59" s="97"/>
       <c r="K59" s="43" t="s">
         <v>283</v>
       </c>
@@ -10563,10 +10563,10 @@
       <c r="M59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N59" s="113" t="s">
+      <c r="N59" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P59" s="104"/>
+      <c r="P59" s="97"/>
       <c r="Q59" s="43" t="s">
         <v>283</v>
       </c>
@@ -10579,7 +10579,7 @@
       <c r="T59" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V59" s="104"/>
+      <c r="V59" s="97"/>
       <c r="W59" s="43" t="s">
         <v>283</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="Z59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB59" s="104"/>
+      <c r="AB59" s="97"/>
       <c r="AC59" s="43" t="s">
         <v>283</v>
       </c>
@@ -10607,7 +10607,7 @@
       </c>
     </row>
     <row r="60" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="104" t="s">
+      <c r="D60" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E60" s="43" t="s">
@@ -10619,10 +10619,10 @@
       <c r="G60" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H60" s="113" t="s">
+      <c r="H60" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J60" s="104" t="s">
+      <c r="J60" s="97" t="s">
         <v>301</v>
       </c>
       <c r="K60" s="43" t="s">
@@ -10634,10 +10634,10 @@
       <c r="M60" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N60" s="113" t="s">
+      <c r="N60" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P60" s="104" t="s">
+      <c r="P60" s="97" t="s">
         <v>301</v>
       </c>
       <c r="Q60" s="43" t="s">
@@ -10652,7 +10652,7 @@
       <c r="T60" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V60" s="104" t="s">
+      <c r="V60" s="97" t="s">
         <v>301</v>
       </c>
       <c r="W60" s="43" t="s">
@@ -10667,7 +10667,7 @@
       <c r="Z60" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB60" s="104" t="s">
+      <c r="AB60" s="97" t="s">
         <v>301</v>
       </c>
       <c r="AC60" s="43" t="s">
@@ -10684,7 +10684,7 @@
       </c>
     </row>
     <row r="61" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="D61" s="104"/>
+      <c r="D61" s="97"/>
       <c r="E61" s="43" t="s">
         <v>282</v>
       </c>
@@ -10694,10 +10694,10 @@
       <c r="G61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="113" t="s">
+      <c r="H61" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J61" s="104"/>
+      <c r="J61" s="97"/>
       <c r="K61" s="43" t="s">
         <v>282</v>
       </c>
@@ -10707,10 +10707,10 @@
       <c r="M61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N61" s="113" t="s">
+      <c r="N61" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P61" s="104"/>
+      <c r="P61" s="97"/>
       <c r="Q61" s="43" t="s">
         <v>282</v>
       </c>
@@ -10723,7 +10723,7 @@
       <c r="T61" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V61" s="104"/>
+      <c r="V61" s="97"/>
       <c r="W61" s="43" t="s">
         <v>282</v>
       </c>
@@ -10736,7 +10736,7 @@
       <c r="Z61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB61" s="104"/>
+      <c r="AB61" s="97"/>
       <c r="AC61" s="43" t="s">
         <v>282</v>
       </c>
@@ -10932,7 +10932,7 @@
       </c>
     </row>
     <row r="72" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D72" s="104" t="s">
+      <c r="D72" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E72" s="42" t="s">
@@ -10941,7 +10941,7 @@
       <c r="F72" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J72" s="104" t="s">
+      <c r="J72" s="97" t="s">
         <v>295</v>
       </c>
       <c r="K72" s="42" t="s">
@@ -10950,7 +10950,7 @@
       <c r="L72" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P72" s="104" t="s">
+      <c r="P72" s="97" t="s">
         <v>295</v>
       </c>
       <c r="Q72" s="42" t="s">
@@ -10959,7 +10959,7 @@
       <c r="R72" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V72" s="104" t="s">
+      <c r="V72" s="97" t="s">
         <v>295</v>
       </c>
       <c r="W72" s="42" t="s">
@@ -10970,28 +10970,28 @@
       </c>
     </row>
     <row r="73" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D73" s="104"/>
+      <c r="D73" s="97"/>
       <c r="E73" s="42" t="s">
         <v>296</v>
       </c>
       <c r="F73" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="J73" s="104"/>
+      <c r="J73" s="97"/>
       <c r="K73" s="42" t="s">
         <v>296</v>
       </c>
       <c r="L73" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P73" s="104"/>
+      <c r="P73" s="97"/>
       <c r="Q73" s="42" t="s">
         <v>296</v>
       </c>
       <c r="R73" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V73" s="104"/>
+      <c r="V73" s="97"/>
       <c r="W73" s="42" t="s">
         <v>296</v>
       </c>
@@ -11000,7 +11000,7 @@
       </c>
     </row>
     <row r="74" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D74" s="104" t="s">
+      <c r="D74" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E74" s="42" t="s">
@@ -11009,7 +11009,7 @@
       <c r="F74" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="J74" s="104" t="s">
+      <c r="J74" s="97" t="s">
         <v>297</v>
       </c>
       <c r="K74" s="42" t="s">
@@ -11018,7 +11018,7 @@
       <c r="L74" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P74" s="104" t="s">
+      <c r="P74" s="97" t="s">
         <v>297</v>
       </c>
       <c r="Q74" s="42" t="s">
@@ -11027,7 +11027,7 @@
       <c r="R74" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="V74" s="104" t="s">
+      <c r="V74" s="97" t="s">
         <v>297</v>
       </c>
       <c r="W74" s="42" t="s">
@@ -11038,28 +11038,28 @@
       </c>
     </row>
     <row r="75" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>275</v>
       </c>
       <c r="F75" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J75" s="104"/>
+      <c r="J75" s="97"/>
       <c r="K75" s="42" t="s">
         <v>275</v>
       </c>
       <c r="L75" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P75" s="104"/>
+      <c r="P75" s="97"/>
       <c r="Q75" s="42" t="s">
         <v>275</v>
       </c>
       <c r="R75" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V75" s="104"/>
+      <c r="V75" s="97"/>
       <c r="W75" s="42" t="s">
         <v>275</v>
       </c>
@@ -11068,7 +11068,7 @@
       </c>
     </row>
     <row r="76" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D76" s="104" t="s">
+      <c r="D76" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E76" s="42" t="s">
@@ -11077,7 +11077,7 @@
       <c r="F76" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="J76" s="104" t="s">
+      <c r="J76" s="97" t="s">
         <v>269</v>
       </c>
       <c r="K76" s="42" t="s">
@@ -11086,7 +11086,7 @@
       <c r="L76" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P76" s="104" t="s">
+      <c r="P76" s="97" t="s">
         <v>269</v>
       </c>
       <c r="Q76" s="42" t="s">
@@ -11095,7 +11095,7 @@
       <c r="R76" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V76" s="104" t="s">
+      <c r="V76" s="97" t="s">
         <v>269</v>
       </c>
       <c r="W76" s="42" t="s">
@@ -11106,28 +11106,28 @@
       </c>
     </row>
     <row r="77" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>274</v>
       </c>
       <c r="F77" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J77" s="104"/>
+      <c r="J77" s="97"/>
       <c r="K77" s="42" t="s">
         <v>274</v>
       </c>
       <c r="L77" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P77" s="104"/>
+      <c r="P77" s="97"/>
       <c r="Q77" s="42" t="s">
         <v>274</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V77" s="104"/>
+      <c r="V77" s="97"/>
       <c r="W77" s="42" t="s">
         <v>274</v>
       </c>
@@ -11136,28 +11136,28 @@
       </c>
     </row>
     <row r="78" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>282</v>
       </c>
       <c r="F78" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="J78" s="104"/>
+      <c r="J78" s="97"/>
       <c r="K78" s="42" t="s">
         <v>282</v>
       </c>
       <c r="L78" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P78" s="104"/>
+      <c r="P78" s="97"/>
       <c r="Q78" s="42" t="s">
         <v>282</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V78" s="104"/>
+      <c r="V78" s="97"/>
       <c r="W78" s="42" t="s">
         <v>282</v>
       </c>
@@ -11166,28 +11166,28 @@
       </c>
     </row>
     <row r="79" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>275</v>
       </c>
       <c r="F79" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J79" s="104"/>
+      <c r="J79" s="97"/>
       <c r="K79" s="42" t="s">
         <v>275</v>
       </c>
       <c r="L79" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P79" s="104"/>
+      <c r="P79" s="97"/>
       <c r="Q79" s="42" t="s">
         <v>275</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V79" s="104"/>
+      <c r="V79" s="97"/>
       <c r="W79" s="42" t="s">
         <v>275</v>
       </c>
@@ -11196,28 +11196,28 @@
       </c>
     </row>
     <row r="80" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>302</v>
       </c>
       <c r="F80" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="J80" s="104"/>
+      <c r="J80" s="97"/>
       <c r="K80" s="42" t="s">
         <v>302</v>
       </c>
       <c r="L80" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P80" s="104"/>
+      <c r="P80" s="97"/>
       <c r="Q80" s="42" t="s">
         <v>302</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V80" s="104"/>
+      <c r="V80" s="97"/>
       <c r="W80" s="42" t="s">
         <v>302</v>
       </c>
@@ -11226,28 +11226,28 @@
       </c>
     </row>
     <row r="81" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>284</v>
       </c>
       <c r="F81" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J81" s="104"/>
+      <c r="J81" s="97"/>
       <c r="K81" s="42" t="s">
         <v>284</v>
       </c>
       <c r="L81" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P81" s="104"/>
+      <c r="P81" s="97"/>
       <c r="Q81" s="42" t="s">
         <v>284</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V81" s="104"/>
+      <c r="V81" s="97"/>
       <c r="W81" s="42" t="s">
         <v>284</v>
       </c>
@@ -11256,28 +11256,28 @@
       </c>
     </row>
     <row r="82" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>285</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="J82" s="104"/>
+      <c r="J82" s="97"/>
       <c r="K82" s="42" t="s">
         <v>285</v>
       </c>
       <c r="L82" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P82" s="104"/>
+      <c r="P82" s="97"/>
       <c r="Q82" s="42" t="s">
         <v>285</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V82" s="104"/>
+      <c r="V82" s="97"/>
       <c r="W82" s="42" t="s">
         <v>285</v>
       </c>
@@ -11286,28 +11286,28 @@
       </c>
     </row>
     <row r="83" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D83" s="104"/>
+      <c r="D83" s="97"/>
       <c r="E83" s="42" t="s">
         <v>286</v>
       </c>
       <c r="F83" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J83" s="104"/>
+      <c r="J83" s="97"/>
       <c r="K83" s="42" t="s">
         <v>286</v>
       </c>
       <c r="L83" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P83" s="104"/>
+      <c r="P83" s="97"/>
       <c r="Q83" s="42" t="s">
         <v>286</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V83" s="104"/>
+      <c r="V83" s="97"/>
       <c r="W83" s="42" t="s">
         <v>286</v>
       </c>
@@ -11316,28 +11316,28 @@
       </c>
     </row>
     <row r="84" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>276</v>
       </c>
       <c r="F84" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="J84" s="104"/>
+      <c r="J84" s="97"/>
       <c r="K84" s="42" t="s">
         <v>276</v>
       </c>
       <c r="L84" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P84" s="104"/>
+      <c r="P84" s="97"/>
       <c r="Q84" s="42" t="s">
         <v>276</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V84" s="104"/>
+      <c r="V84" s="97"/>
       <c r="W84" s="42" t="s">
         <v>276</v>
       </c>
@@ -11346,28 +11346,28 @@
       </c>
     </row>
     <row r="85" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D85" s="104"/>
+      <c r="D85" s="97"/>
       <c r="E85" s="42" t="s">
         <v>277</v>
       </c>
       <c r="F85" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J85" s="104"/>
+      <c r="J85" s="97"/>
       <c r="K85" s="42" t="s">
         <v>277</v>
       </c>
       <c r="L85" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P85" s="104"/>
+      <c r="P85" s="97"/>
       <c r="Q85" s="42" t="s">
         <v>277</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V85" s="104"/>
+      <c r="V85" s="97"/>
       <c r="W85" s="42" t="s">
         <v>277</v>
       </c>
@@ -11376,28 +11376,28 @@
       </c>
     </row>
     <row r="86" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>283</v>
       </c>
       <c r="F86" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="J86" s="104"/>
+      <c r="J86" s="97"/>
       <c r="K86" s="42" t="s">
         <v>283</v>
       </c>
       <c r="L86" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P86" s="104"/>
+      <c r="P86" s="97"/>
       <c r="Q86" s="42" t="s">
         <v>283</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V86" s="104"/>
+      <c r="V86" s="97"/>
       <c r="W86" s="42" t="s">
         <v>283</v>
       </c>
@@ -11406,28 +11406,28 @@
       </c>
     </row>
     <row r="87" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D87" s="104"/>
+      <c r="D87" s="97"/>
       <c r="E87" s="42" t="s">
         <v>278</v>
       </c>
       <c r="F87" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="J87" s="104"/>
+      <c r="J87" s="97"/>
       <c r="K87" s="42" t="s">
         <v>278</v>
       </c>
       <c r="L87" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P87" s="104"/>
+      <c r="P87" s="97"/>
       <c r="Q87" s="42" t="s">
         <v>278</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V87" s="104"/>
+      <c r="V87" s="97"/>
       <c r="W87" s="42" t="s">
         <v>278</v>
       </c>
@@ -11436,7 +11436,7 @@
       </c>
     </row>
     <row r="88" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D88" s="104" t="s">
+      <c r="D88" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E88" s="42" t="s">
@@ -11445,7 +11445,7 @@
       <c r="F88" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J88" s="104" t="s">
+      <c r="J88" s="97" t="s">
         <v>298</v>
       </c>
       <c r="K88" s="42" t="s">
@@ -11454,7 +11454,7 @@
       <c r="L88" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P88" s="104" t="s">
+      <c r="P88" s="97" t="s">
         <v>298</v>
       </c>
       <c r="Q88" s="42" t="s">
@@ -11463,7 +11463,7 @@
       <c r="R88" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V88" s="104" t="s">
+      <c r="V88" s="97" t="s">
         <v>298</v>
       </c>
       <c r="W88" s="42" t="s">
@@ -11474,28 +11474,28 @@
       </c>
     </row>
     <row r="89" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>287</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J89" s="104"/>
+      <c r="J89" s="97"/>
       <c r="K89" s="42" t="s">
         <v>287</v>
       </c>
       <c r="L89" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P89" s="104"/>
+      <c r="P89" s="97"/>
       <c r="Q89" s="42" t="s">
         <v>287</v>
       </c>
       <c r="R89" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V89" s="104"/>
+      <c r="V89" s="97"/>
       <c r="W89" s="42" t="s">
         <v>287</v>
       </c>
@@ -11504,7 +11504,7 @@
       </c>
     </row>
     <row r="90" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D90" s="104" t="s">
+      <c r="D90" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E90" s="42" t="s">
@@ -11513,7 +11513,7 @@
       <c r="F90" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J90" s="104" t="s">
+      <c r="J90" s="97" t="s">
         <v>299</v>
       </c>
       <c r="K90" s="42" t="s">
@@ -11522,7 +11522,7 @@
       <c r="L90" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P90" s="104" t="s">
+      <c r="P90" s="97" t="s">
         <v>299</v>
       </c>
       <c r="Q90" s="42" t="s">
@@ -11531,7 +11531,7 @@
       <c r="R90" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="V90" s="104" t="s">
+      <c r="V90" s="97" t="s">
         <v>299</v>
       </c>
       <c r="W90" s="42" t="s">
@@ -11542,28 +11542,28 @@
       </c>
     </row>
     <row r="91" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D91" s="104"/>
+      <c r="D91" s="97"/>
       <c r="E91" s="42" t="s">
         <v>281</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J91" s="104"/>
+      <c r="J91" s="97"/>
       <c r="K91" s="42" t="s">
         <v>281</v>
       </c>
       <c r="L91" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P91" s="104"/>
+      <c r="P91" s="97"/>
       <c r="Q91" s="42" t="s">
         <v>281</v>
       </c>
       <c r="R91" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V91" s="104"/>
+      <c r="V91" s="97"/>
       <c r="W91" s="42" t="s">
         <v>281</v>
       </c>
@@ -11572,28 +11572,28 @@
       </c>
     </row>
     <row r="92" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D92" s="104"/>
+      <c r="D92" s="97"/>
       <c r="E92" s="42" t="s">
         <v>277</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J92" s="104"/>
+      <c r="J92" s="97"/>
       <c r="K92" s="42" t="s">
         <v>277</v>
       </c>
       <c r="L92" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P92" s="104"/>
+      <c r="P92" s="97"/>
       <c r="Q92" s="42" t="s">
         <v>277</v>
       </c>
       <c r="R92" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V92" s="104"/>
+      <c r="V92" s="97"/>
       <c r="W92" s="42" t="s">
         <v>277</v>
       </c>
@@ -11602,28 +11602,28 @@
       </c>
     </row>
     <row r="93" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D93" s="104"/>
+      <c r="D93" s="97"/>
       <c r="E93" s="42" t="s">
         <v>283</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J93" s="104"/>
+      <c r="J93" s="97"/>
       <c r="K93" s="42" t="s">
         <v>283</v>
       </c>
       <c r="L93" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="P93" s="104"/>
+      <c r="P93" s="97"/>
       <c r="Q93" s="42" t="s">
         <v>283</v>
       </c>
       <c r="R93" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V93" s="104"/>
+      <c r="V93" s="97"/>
       <c r="W93" s="42" t="s">
         <v>283</v>
       </c>
@@ -11632,28 +11632,28 @@
       </c>
     </row>
     <row r="94" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D94" s="104"/>
+      <c r="D94" s="97"/>
       <c r="E94" s="42" t="s">
         <v>276</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J94" s="104"/>
+      <c r="J94" s="97"/>
       <c r="K94" s="42" t="s">
         <v>276</v>
       </c>
       <c r="L94" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="P94" s="104"/>
+      <c r="P94" s="97"/>
       <c r="Q94" s="42" t="s">
         <v>276</v>
       </c>
       <c r="R94" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="V94" s="104"/>
+      <c r="V94" s="97"/>
       <c r="W94" s="42" t="s">
         <v>276</v>
       </c>
@@ -11662,28 +11662,28 @@
       </c>
     </row>
     <row r="95" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D95" s="104"/>
+      <c r="D95" s="97"/>
       <c r="E95" s="42" t="s">
         <v>278</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J95" s="104"/>
+      <c r="J95" s="97"/>
       <c r="K95" s="42" t="s">
         <v>278</v>
       </c>
       <c r="L95" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="P95" s="104"/>
+      <c r="P95" s="97"/>
       <c r="Q95" s="42" t="s">
         <v>278</v>
       </c>
       <c r="R95" s="53" t="s">
         <v>799</v>
       </c>
-      <c r="V95" s="104"/>
+      <c r="V95" s="97"/>
       <c r="W95" s="42" t="s">
         <v>278</v>
       </c>
@@ -11774,7 +11774,7 @@
       <c r="E98" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F98" s="113" t="s">
+      <c r="F98" s="96" t="s">
         <v>11</v>
       </c>
       <c r="J98" s="48" t="s">
@@ -11812,7 +11812,7 @@
       <c r="E99" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F99" s="113" t="s">
+      <c r="F99" s="96" t="s">
         <v>11</v>
       </c>
       <c r="J99" s="48" t="s">
@@ -11821,7 +11821,7 @@
       <c r="K99" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="L99" s="113" t="s">
+      <c r="L99" s="96" t="s">
         <v>11</v>
       </c>
       <c r="P99" s="48" t="s">
@@ -11844,25 +11844,25 @@
       </c>
     </row>
     <row r="100" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D100" s="104" t="s">
+      <c r="D100" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E100" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="F100" s="113" t="s">
+      <c r="F100" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J100" s="104" t="s">
+      <c r="J100" s="97" t="s">
         <v>300</v>
       </c>
       <c r="K100" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="L100" s="113" t="s">
+      <c r="L100" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P100" s="104" t="s">
+      <c r="P100" s="97" t="s">
         <v>300</v>
       </c>
       <c r="Q100" s="43" t="s">
@@ -11871,7 +11871,7 @@
       <c r="R100" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V100" s="104" t="s">
+      <c r="V100" s="97" t="s">
         <v>300</v>
       </c>
       <c r="W100" s="43" t="s">
@@ -11882,28 +11882,28 @@
       </c>
     </row>
     <row r="101" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="F101" s="113" t="s">
+      <c r="F101" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J101" s="104"/>
+      <c r="J101" s="97"/>
       <c r="K101" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="L101" s="113" t="s">
+      <c r="L101" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P101" s="104"/>
+      <c r="P101" s="97"/>
       <c r="Q101" s="43" t="s">
         <v>282</v>
       </c>
       <c r="R101" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V101" s="104"/>
+      <c r="V101" s="97"/>
       <c r="W101" s="43" t="s">
         <v>282</v>
       </c>
@@ -11912,28 +11912,28 @@
       </c>
     </row>
     <row r="102" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D102" s="104"/>
+      <c r="D102" s="97"/>
       <c r="E102" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="F102" s="113" t="s">
+      <c r="F102" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J102" s="104"/>
+      <c r="J102" s="97"/>
       <c r="K102" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="L102" s="113" t="s">
+      <c r="L102" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P102" s="104"/>
+      <c r="P102" s="97"/>
       <c r="Q102" s="43" t="s">
         <v>302</v>
       </c>
       <c r="R102" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V102" s="104"/>
+      <c r="V102" s="97"/>
       <c r="W102" s="43" t="s">
         <v>302</v>
       </c>
@@ -11942,28 +11942,28 @@
       </c>
     </row>
     <row r="103" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D103" s="104"/>
+      <c r="D103" s="97"/>
       <c r="E103" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="F103" s="113" t="s">
+      <c r="F103" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J103" s="104"/>
+      <c r="J103" s="97"/>
       <c r="K103" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="L103" s="113" t="s">
+      <c r="L103" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P103" s="104"/>
+      <c r="P103" s="97"/>
       <c r="Q103" s="43" t="s">
         <v>285</v>
       </c>
       <c r="R103" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V103" s="104"/>
+      <c r="V103" s="97"/>
       <c r="W103" s="43" t="s">
         <v>285</v>
       </c>
@@ -11972,28 +11972,28 @@
       </c>
     </row>
     <row r="104" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D104" s="104"/>
+      <c r="D104" s="97"/>
       <c r="E104" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="F104" s="113" t="s">
+      <c r="F104" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J104" s="104"/>
+      <c r="J104" s="97"/>
       <c r="K104" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="L104" s="113" t="s">
+      <c r="L104" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P104" s="104"/>
+      <c r="P104" s="97"/>
       <c r="Q104" s="43" t="s">
         <v>276</v>
       </c>
       <c r="R104" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V104" s="104"/>
+      <c r="V104" s="97"/>
       <c r="W104" s="43" t="s">
         <v>276</v>
       </c>
@@ -12002,28 +12002,28 @@
       </c>
     </row>
     <row r="105" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D105" s="104"/>
+      <c r="D105" s="97"/>
       <c r="E105" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="F105" s="113" t="s">
+      <c r="F105" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J105" s="104"/>
+      <c r="J105" s="97"/>
       <c r="K105" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="L105" s="113" t="s">
+      <c r="L105" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P105" s="104"/>
+      <c r="P105" s="97"/>
       <c r="Q105" s="43" t="s">
         <v>283</v>
       </c>
       <c r="R105" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V105" s="104"/>
+      <c r="V105" s="97"/>
       <c r="W105" s="43" t="s">
         <v>283</v>
       </c>
@@ -12032,25 +12032,25 @@
       </c>
     </row>
     <row r="106" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D106" s="104" t="s">
+      <c r="D106" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E106" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="F106" s="113" t="s">
+      <c r="F106" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J106" s="104" t="s">
+      <c r="J106" s="97" t="s">
         <v>301</v>
       </c>
       <c r="K106" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="L106" s="113" t="s">
+      <c r="L106" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P106" s="104" t="s">
+      <c r="P106" s="97" t="s">
         <v>301</v>
       </c>
       <c r="Q106" s="43" t="s">
@@ -12059,7 +12059,7 @@
       <c r="R106" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V106" s="104" t="s">
+      <c r="V106" s="97" t="s">
         <v>301</v>
       </c>
       <c r="W106" s="43" t="s">
@@ -12070,28 +12070,28 @@
       </c>
     </row>
     <row r="107" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D107" s="104"/>
+      <c r="D107" s="97"/>
       <c r="E107" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="F107" s="113" t="s">
+      <c r="F107" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="J107" s="104"/>
+      <c r="J107" s="97"/>
       <c r="K107" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="L107" s="113" t="s">
+      <c r="L107" s="96" t="s">
         <v>800</v>
       </c>
-      <c r="P107" s="104"/>
+      <c r="P107" s="97"/>
       <c r="Q107" s="43" t="s">
         <v>282</v>
       </c>
       <c r="R107" s="53" t="s">
         <v>800</v>
       </c>
-      <c r="V107" s="104"/>
+      <c r="V107" s="97"/>
       <c r="W107" s="43" t="s">
         <v>282</v>
       </c>
@@ -12108,21 +12108,93 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="98">
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="D25:D36"/>
+    <mergeCell ref="J25:J36"/>
+    <mergeCell ref="P25:P36"/>
+    <mergeCell ref="D37:D44"/>
+    <mergeCell ref="J37:J44"/>
+    <mergeCell ref="P37:P44"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="J45:J48"/>
+    <mergeCell ref="P45:P48"/>
+    <mergeCell ref="D54:D59"/>
+    <mergeCell ref="J54:J59"/>
+    <mergeCell ref="P54:P59"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="P60:P61"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="P72:P73"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="D76:D87"/>
+    <mergeCell ref="J76:J87"/>
+    <mergeCell ref="P76:P87"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="P88:P89"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="P106:P107"/>
+    <mergeCell ref="D90:D95"/>
+    <mergeCell ref="J90:J95"/>
+    <mergeCell ref="P90:P95"/>
+    <mergeCell ref="D100:D105"/>
+    <mergeCell ref="J100:J105"/>
+    <mergeCell ref="P100:P105"/>
+    <mergeCell ref="V54:V59"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="V18:V19"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB25:AB36"/>
+    <mergeCell ref="AB37:AB44"/>
+    <mergeCell ref="AD17:AF17"/>
+    <mergeCell ref="AB18:AB19"/>
+    <mergeCell ref="AD18:AF18"/>
+    <mergeCell ref="AD19:AF19"/>
+    <mergeCell ref="AD20:AF20"/>
     <mergeCell ref="AB60:AB61"/>
     <mergeCell ref="V90:V95"/>
     <mergeCell ref="V100:V105"/>
     <mergeCell ref="V106:V107"/>
     <mergeCell ref="AB17:AC17"/>
-    <mergeCell ref="AD17:AF17"/>
-    <mergeCell ref="AB18:AB19"/>
-    <mergeCell ref="AD18:AF18"/>
-    <mergeCell ref="AD19:AF19"/>
-    <mergeCell ref="AD20:AF20"/>
-    <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB25:AB36"/>
-    <mergeCell ref="AB37:AB44"/>
     <mergeCell ref="AB45:AB48"/>
     <mergeCell ref="AB54:AB59"/>
     <mergeCell ref="V60:V61"/>
@@ -12134,78 +12206,6 @@
     <mergeCell ref="V25:V36"/>
     <mergeCell ref="V37:V44"/>
     <mergeCell ref="V45:V48"/>
-    <mergeCell ref="V54:V59"/>
-    <mergeCell ref="X20:Z20"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="V18:V19"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="P106:P107"/>
-    <mergeCell ref="D90:D95"/>
-    <mergeCell ref="J90:J95"/>
-    <mergeCell ref="P90:P95"/>
-    <mergeCell ref="D100:D105"/>
-    <mergeCell ref="J100:J105"/>
-    <mergeCell ref="P100:P105"/>
-    <mergeCell ref="D76:D87"/>
-    <mergeCell ref="J76:J87"/>
-    <mergeCell ref="P76:P87"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="P88:P89"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="P72:P73"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="D54:D59"/>
-    <mergeCell ref="J54:J59"/>
-    <mergeCell ref="P54:P59"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="P60:P61"/>
-    <mergeCell ref="D37:D44"/>
-    <mergeCell ref="J37:J44"/>
-    <mergeCell ref="P37:P44"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="J45:J48"/>
-    <mergeCell ref="P45:P48"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="D25:D36"/>
-    <mergeCell ref="J25:J36"/>
-    <mergeCell ref="P25:P36"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="P17:Q17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -12322,52 +12322,52 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="97" t="s">
+      <c r="D15" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="96" t="s">
+      <c r="E15" s="98"/>
+      <c r="F15" s="99" t="s">
         <v>689</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="106" t="s">
+      <c r="F16" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="107"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="106" t="s">
+      <c r="G16" s="108"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="107" t="s">
         <v>290</v>
       </c>
-      <c r="J16" s="107"/>
-      <c r="K16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="109"/>
     </row>
     <row r="17" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D17" s="99"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F17" s="103" t="s">
+      <c r="F17" s="105" t="s">
         <v>690</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="105" t="s">
+      <c r="G17" s="105"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="106" t="s">
         <v>690</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="21"/>
     </row>
     <row r="18" spans="4:1160" x14ac:dyDescent="0.25">
@@ -12377,16 +12377,16 @@
       <c r="E18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F18" s="103" t="s">
+      <c r="F18" s="105" t="s">
         <v>691</v>
       </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="105" t="s">
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
       <c r="L18" s="21"/>
     </row>
     <row r="19" spans="4:1160" x14ac:dyDescent="0.25">
@@ -12396,16 +12396,16 @@
       <c r="E19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F19" s="103" t="s">
+      <c r="F19" s="105" t="s">
         <v>692</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="105" t="s">
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
       <c r="L19" s="21"/>
     </row>
     <row r="20" spans="4:1160" x14ac:dyDescent="0.25">
@@ -12415,23 +12415,23 @@
       <c r="E20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="F20" s="105" t="s">
         <v>693</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="105" t="s">
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
       <c r="L20" s="21"/>
     </row>
     <row r="21" spans="4:1160" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="104"/>
+      <c r="E21" s="97"/>
       <c r="F21" s="50" t="s">
         <v>305</v>
       </c>
@@ -13628,7 +13628,7 @@
       <c r="L22" s="21"/>
     </row>
     <row r="23" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E23" s="42" t="s">
@@ -13657,7 +13657,7 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D24" s="104"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="42" t="s">
         <v>274</v>
       </c>
@@ -13684,7 +13684,7 @@
       <c r="L24" s="21"/>
     </row>
     <row r="25" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D25" s="104"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="42" t="s">
         <v>282</v>
       </c>
@@ -13711,7 +13711,7 @@
       <c r="L25" s="21"/>
     </row>
     <row r="26" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>275</v>
       </c>
@@ -13738,7 +13738,7 @@
       <c r="L26" s="36"/>
     </row>
     <row r="27" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>302</v>
       </c>
@@ -13765,7 +13765,7 @@
       <c r="L27" s="33"/>
     </row>
     <row r="28" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>284</v>
       </c>
@@ -13792,7 +13792,7 @@
       <c r="L28" s="33"/>
     </row>
     <row r="29" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>285</v>
       </c>
@@ -13819,7 +13819,7 @@
       <c r="L29" s="33"/>
     </row>
     <row r="30" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>286</v>
       </c>
@@ -13846,7 +13846,7 @@
       <c r="L30" s="33"/>
     </row>
     <row r="31" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>276</v>
       </c>
@@ -13873,7 +13873,7 @@
       <c r="L31" s="33"/>
     </row>
     <row r="32" spans="4:1160" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>277</v>
       </c>
@@ -13900,7 +13900,7 @@
       <c r="L32" s="33"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>283</v>
       </c>
@@ -13927,7 +13927,7 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>278</v>
       </c>
@@ -13954,7 +13954,7 @@
       <c r="L34" s="33"/>
     </row>
     <row r="35" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="104" t="s">
+      <c r="D35" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="42" t="s">
@@ -13981,7 +13981,7 @@
       <c r="L35" s="33"/>
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D36" s="104"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="42" t="s">
         <v>280</v>
       </c>
@@ -14006,7 +14006,7 @@
       <c r="L36" s="38"/>
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D37" s="104"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="42" t="s">
         <v>287</v>
       </c>
@@ -14031,7 +14031,7 @@
       <c r="L37" s="38"/>
     </row>
     <row r="38" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>281</v>
       </c>
@@ -14056,7 +14056,7 @@
       <c r="L38" s="38"/>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>276</v>
       </c>
@@ -14081,7 +14081,7 @@
       <c r="L39" s="38"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>277</v>
       </c>
@@ -14106,7 +14106,7 @@
       <c r="L40" s="38"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>283</v>
       </c>
@@ -14130,7 +14130,7 @@
       </c>
     </row>
     <row r="42" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>278</v>
       </c>
@@ -14154,7 +14154,7 @@
       </c>
     </row>
     <row r="43" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D43" s="104" t="s">
+      <c r="D43" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="42" t="s">
@@ -14182,7 +14182,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D44" s="104"/>
+      <c r="D44" s="97"/>
       <c r="E44" s="42" t="s">
         <v>274</v>
       </c>
@@ -14208,7 +14208,7 @@
       </c>
     </row>
     <row r="45" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D45" s="104"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="42" t="s">
         <v>282</v>
       </c>
@@ -14234,7 +14234,7 @@
       </c>
     </row>
     <row r="46" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>275</v>
       </c>
@@ -14364,7 +14364,7 @@
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E51" s="43" t="s">
@@ -14390,7 +14390,7 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D52" s="104"/>
+      <c r="D52" s="97"/>
       <c r="E52" s="43" t="s">
         <v>282</v>
       </c>
@@ -14414,7 +14414,7 @@
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D53" s="104"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="43" t="s">
         <v>302</v>
       </c>
@@ -14438,7 +14438,7 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D54" s="104"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="43" t="s">
         <v>285</v>
       </c>
@@ -14462,7 +14462,7 @@
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>276</v>
       </c>
@@ -14486,7 +14486,7 @@
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>283</v>
       </c>
@@ -14510,7 +14510,7 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D57" s="104" t="s">
+      <c r="D57" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E57" s="43" t="s">
@@ -14536,7 +14536,7 @@
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D58" s="104"/>
+      <c r="D58" s="97"/>
       <c r="E58" s="43" t="s">
         <v>282</v>
       </c>
@@ -14612,7 +14612,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="104" t="s">
+      <c r="D67" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E67" s="42" t="s">
@@ -14624,7 +14624,7 @@
       </c>
     </row>
     <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="104"/>
+      <c r="D68" s="97"/>
       <c r="E68" s="42" t="s">
         <v>296</v>
       </c>
@@ -14634,7 +14634,7 @@
       </c>
     </row>
     <row r="69" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="104" t="s">
+      <c r="D69" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E69" s="42" t="s">
@@ -14646,7 +14646,7 @@
       </c>
     </row>
     <row r="70" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="104"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="42" t="s">
         <v>275</v>
       </c>
@@ -14656,7 +14656,7 @@
       </c>
     </row>
     <row r="71" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E71" s="42" t="s">
@@ -14668,7 +14668,7 @@
       </c>
     </row>
     <row r="72" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="104"/>
+      <c r="D72" s="97"/>
       <c r="E72" s="42" t="s">
         <v>274</v>
       </c>
@@ -14678,7 +14678,7 @@
       </c>
     </row>
     <row r="73" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D73" s="104"/>
+      <c r="D73" s="97"/>
       <c r="E73" s="42" t="s">
         <v>282</v>
       </c>
@@ -14688,7 +14688,7 @@
       </c>
     </row>
     <row r="74" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D74" s="104"/>
+      <c r="D74" s="97"/>
       <c r="E74" s="42" t="s">
         <v>275</v>
       </c>
@@ -14698,7 +14698,7 @@
       </c>
     </row>
     <row r="75" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>302</v>
       </c>
@@ -14708,7 +14708,7 @@
       </c>
     </row>
     <row r="76" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D76" s="104"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="42" t="s">
         <v>284</v>
       </c>
@@ -14718,7 +14718,7 @@
       </c>
     </row>
     <row r="77" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>285</v>
       </c>
@@ -14728,7 +14728,7 @@
       </c>
     </row>
     <row r="78" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>286</v>
       </c>
@@ -14738,7 +14738,7 @@
       </c>
     </row>
     <row r="79" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>276</v>
       </c>
@@ -14748,7 +14748,7 @@
       </c>
     </row>
     <row r="80" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>277</v>
       </c>
@@ -14758,7 +14758,7 @@
       </c>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>283</v>
       </c>
@@ -14768,7 +14768,7 @@
       </c>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>278</v>
       </c>
@@ -14778,7 +14778,7 @@
       </c>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="104" t="s">
+      <c r="D83" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E83" s="42" t="s">
@@ -14789,7 +14789,7 @@
       </c>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>287</v>
       </c>
@@ -14798,7 +14798,7 @@
       </c>
     </row>
     <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="104" t="s">
+      <c r="D85" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E85" s="42" t="s">
@@ -14809,7 +14809,7 @@
       </c>
     </row>
     <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>281</v>
       </c>
@@ -14818,7 +14818,7 @@
       </c>
     </row>
     <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="104"/>
+      <c r="D87" s="97"/>
       <c r="E87" s="42" t="s">
         <v>277</v>
       </c>
@@ -14827,7 +14827,7 @@
       </c>
     </row>
     <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="104"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="42" t="s">
         <v>283</v>
       </c>
@@ -14836,7 +14836,7 @@
       </c>
     </row>
     <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>276</v>
       </c>
@@ -14845,7 +14845,7 @@
       </c>
     </row>
     <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="104"/>
+      <c r="D90" s="97"/>
       <c r="E90" s="42" t="s">
         <v>278</v>
       </c>
@@ -14887,7 +14887,7 @@
       </c>
     </row>
     <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="104" t="s">
+      <c r="D94" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E94" s="43" t="s">
@@ -14898,7 +14898,7 @@
       </c>
     </row>
     <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="104"/>
+      <c r="D95" s="97"/>
       <c r="E95" s="43" t="s">
         <v>282</v>
       </c>
@@ -14907,7 +14907,7 @@
       </c>
     </row>
     <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="104"/>
+      <c r="D96" s="97"/>
       <c r="E96" s="43" t="s">
         <v>302</v>
       </c>
@@ -14916,7 +14916,7 @@
       </c>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="104"/>
+      <c r="D97" s="97"/>
       <c r="E97" s="43" t="s">
         <v>285</v>
       </c>
@@ -14925,7 +14925,7 @@
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="104"/>
+      <c r="D98" s="97"/>
       <c r="E98" s="43" t="s">
         <v>276</v>
       </c>
@@ -14934,7 +14934,7 @@
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="104"/>
+      <c r="D99" s="97"/>
       <c r="E99" s="43" t="s">
         <v>283</v>
       </c>
@@ -14943,7 +14943,7 @@
       </c>
     </row>
     <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="104" t="s">
+      <c r="D100" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E100" s="43" t="s">
@@ -14954,7 +14954,7 @@
       </c>
     </row>
     <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>282</v>
       </c>
@@ -14971,6 +14971,23 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D94:D99"/>
+    <mergeCell ref="D71:D82"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="D51:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:D34"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:K15"/>
     <mergeCell ref="F18:H18"/>
@@ -14980,23 +14997,6 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="I16:K16"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D23:D34"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="D51:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D35:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D94:D99"/>
-    <mergeCell ref="D71:D82"/>
-    <mergeCell ref="D83:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -15128,52 +15128,52 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D15" s="97" t="s">
+      <c r="D15" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="96" t="s">
+      <c r="E15" s="98"/>
+      <c r="F15" s="99" t="s">
         <v>689</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="100" t="s">
+      <c r="F16" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="100" t="s">
+      <c r="G16" s="103"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="J16" s="101"/>
-      <c r="K16" s="102"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="104"/>
     </row>
     <row r="17" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D17" s="99"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F17" s="105" t="s">
+      <c r="F17" s="106" t="s">
         <v>690</v>
       </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105" t="s">
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106" t="s">
         <v>690</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="21"/>
     </row>
     <row r="18" spans="4:12" x14ac:dyDescent="0.25">
@@ -15183,16 +15183,16 @@
       <c r="E18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105" t="s">
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
       <c r="L18" s="21"/>
     </row>
     <row r="19" spans="4:12" x14ac:dyDescent="0.25">
@@ -15202,16 +15202,16 @@
       <c r="E19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105" t="s">
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
       <c r="L19" s="21"/>
     </row>
     <row r="20" spans="4:12" x14ac:dyDescent="0.25">
@@ -15221,23 +15221,23 @@
       <c r="E20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105" t="s">
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
       <c r="L20" s="21"/>
     </row>
     <row r="21" spans="4:12" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="104"/>
+      <c r="E21" s="97"/>
       <c r="F21" s="50" t="s">
         <v>305</v>
       </c>
@@ -15286,7 +15286,7 @@
       <c r="L22" s="21"/>
     </row>
     <row r="23" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E23" s="42" t="s">
@@ -15315,7 +15315,7 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D24" s="104"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="42" t="s">
         <v>274</v>
       </c>
@@ -15342,7 +15342,7 @@
       <c r="L24" s="21"/>
     </row>
     <row r="25" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D25" s="104"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="42" t="s">
         <v>282</v>
       </c>
@@ -15369,7 +15369,7 @@
       <c r="L25" s="21"/>
     </row>
     <row r="26" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>275</v>
       </c>
@@ -15396,7 +15396,7 @@
       <c r="L26" s="36"/>
     </row>
     <row r="27" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>302</v>
       </c>
@@ -15423,7 +15423,7 @@
       <c r="L27" s="33"/>
     </row>
     <row r="28" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>284</v>
       </c>
@@ -15450,7 +15450,7 @@
       <c r="L28" s="33"/>
     </row>
     <row r="29" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>285</v>
       </c>
@@ -15477,7 +15477,7 @@
       <c r="L29" s="33"/>
     </row>
     <row r="30" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>286</v>
       </c>
@@ -15504,7 +15504,7 @@
       <c r="L30" s="33"/>
     </row>
     <row r="31" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>276</v>
       </c>
@@ -15531,7 +15531,7 @@
       <c r="L31" s="33"/>
     </row>
     <row r="32" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>277</v>
       </c>
@@ -15558,7 +15558,7 @@
       <c r="L32" s="33"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>283</v>
       </c>
@@ -15585,7 +15585,7 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>278</v>
       </c>
@@ -15612,7 +15612,7 @@
       <c r="L34" s="33"/>
     </row>
     <row r="35" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="104" t="s">
+      <c r="D35" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="42" t="s">
@@ -15639,7 +15639,7 @@
       <c r="L35" s="33"/>
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D36" s="104"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="42" t="s">
         <v>280</v>
       </c>
@@ -15664,7 +15664,7 @@
       <c r="L36" s="38"/>
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D37" s="104"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="42" t="s">
         <v>287</v>
       </c>
@@ -15689,7 +15689,7 @@
       <c r="L37" s="38"/>
     </row>
     <row r="38" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>281</v>
       </c>
@@ -15714,7 +15714,7 @@
       <c r="L38" s="38"/>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>276</v>
       </c>
@@ -15739,7 +15739,7 @@
       <c r="L39" s="38"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>277</v>
       </c>
@@ -15764,7 +15764,7 @@
       <c r="L40" s="38"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>283</v>
       </c>
@@ -15788,7 +15788,7 @@
       </c>
     </row>
     <row r="42" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>278</v>
       </c>
@@ -15812,7 +15812,7 @@
       </c>
     </row>
     <row r="43" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D43" s="104" t="s">
+      <c r="D43" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="42" t="s">
@@ -15840,7 +15840,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D44" s="104"/>
+      <c r="D44" s="97"/>
       <c r="E44" s="42" t="s">
         <v>274</v>
       </c>
@@ -15866,7 +15866,7 @@
       </c>
     </row>
     <row r="45" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D45" s="104"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="42" t="s">
         <v>282</v>
       </c>
@@ -15892,7 +15892,7 @@
       </c>
     </row>
     <row r="46" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>275</v>
       </c>
@@ -16022,7 +16022,7 @@
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E51" s="43" t="s">
@@ -16048,7 +16048,7 @@
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D52" s="104"/>
+      <c r="D52" s="97"/>
       <c r="E52" s="43" t="s">
         <v>282</v>
       </c>
@@ -16072,7 +16072,7 @@
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D53" s="104"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="43" t="s">
         <v>302</v>
       </c>
@@ -16096,7 +16096,7 @@
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D54" s="104"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="43" t="s">
         <v>285</v>
       </c>
@@ -16120,7 +16120,7 @@
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>276</v>
       </c>
@@ -16144,7 +16144,7 @@
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>283</v>
       </c>
@@ -16168,7 +16168,7 @@
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D57" s="104" t="s">
+      <c r="D57" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E57" s="43" t="s">
@@ -16194,7 +16194,7 @@
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D58" s="104"/>
+      <c r="D58" s="97"/>
       <c r="E58" s="43" t="s">
         <v>282</v>
       </c>
@@ -16271,7 +16271,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="104" t="s">
+      <c r="D67" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E67" s="42" t="s">
@@ -16283,7 +16283,7 @@
       </c>
     </row>
     <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="104"/>
+      <c r="D68" s="97"/>
       <c r="E68" s="42" t="s">
         <v>296</v>
       </c>
@@ -16293,7 +16293,7 @@
       </c>
     </row>
     <row r="69" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="104" t="s">
+      <c r="D69" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E69" s="42" t="s">
@@ -16305,7 +16305,7 @@
       </c>
     </row>
     <row r="70" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="104"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="42" t="s">
         <v>275</v>
       </c>
@@ -16315,7 +16315,7 @@
       </c>
     </row>
     <row r="71" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E71" s="42" t="s">
@@ -16327,7 +16327,7 @@
       </c>
     </row>
     <row r="72" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="104"/>
+      <c r="D72" s="97"/>
       <c r="E72" s="42" t="s">
         <v>274</v>
       </c>
@@ -16337,7 +16337,7 @@
       </c>
     </row>
     <row r="73" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D73" s="104"/>
+      <c r="D73" s="97"/>
       <c r="E73" s="42" t="s">
         <v>282</v>
       </c>
@@ -16347,7 +16347,7 @@
       </c>
     </row>
     <row r="74" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D74" s="104"/>
+      <c r="D74" s="97"/>
       <c r="E74" s="42" t="s">
         <v>275</v>
       </c>
@@ -16357,7 +16357,7 @@
       </c>
     </row>
     <row r="75" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>302</v>
       </c>
@@ -16367,7 +16367,7 @@
       </c>
     </row>
     <row r="76" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D76" s="104"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="42" t="s">
         <v>284</v>
       </c>
@@ -16377,7 +16377,7 @@
       </c>
     </row>
     <row r="77" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>285</v>
       </c>
@@ -16387,7 +16387,7 @@
       </c>
     </row>
     <row r="78" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>286</v>
       </c>
@@ -16397,7 +16397,7 @@
       </c>
     </row>
     <row r="79" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>276</v>
       </c>
@@ -16407,7 +16407,7 @@
       </c>
     </row>
     <row r="80" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>277</v>
       </c>
@@ -16417,7 +16417,7 @@
       </c>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>283</v>
       </c>
@@ -16427,7 +16427,7 @@
       </c>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>278</v>
       </c>
@@ -16437,7 +16437,7 @@
       </c>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="104" t="s">
+      <c r="D83" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E83" s="42" t="s">
@@ -16448,7 +16448,7 @@
       </c>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>287</v>
       </c>
@@ -16457,7 +16457,7 @@
       </c>
     </row>
     <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="104" t="s">
+      <c r="D85" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E85" s="42" t="s">
@@ -16468,7 +16468,7 @@
       </c>
     </row>
     <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>281</v>
       </c>
@@ -16477,7 +16477,7 @@
       </c>
     </row>
     <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="104"/>
+      <c r="D87" s="97"/>
       <c r="E87" s="42" t="s">
         <v>277</v>
       </c>
@@ -16486,7 +16486,7 @@
       </c>
     </row>
     <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="104"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="42" t="s">
         <v>283</v>
       </c>
@@ -16495,7 +16495,7 @@
       </c>
     </row>
     <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>276</v>
       </c>
@@ -16504,7 +16504,7 @@
       </c>
     </row>
     <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="104"/>
+      <c r="D90" s="97"/>
       <c r="E90" s="42" t="s">
         <v>278</v>
       </c>
@@ -16546,7 +16546,7 @@
       </c>
     </row>
     <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="104" t="s">
+      <c r="D94" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E94" s="43" t="s">
@@ -16557,7 +16557,7 @@
       </c>
     </row>
     <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="104"/>
+      <c r="D95" s="97"/>
       <c r="E95" s="43" t="s">
         <v>282</v>
       </c>
@@ -16566,7 +16566,7 @@
       </c>
     </row>
     <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="104"/>
+      <c r="D96" s="97"/>
       <c r="E96" s="43" t="s">
         <v>302</v>
       </c>
@@ -16575,7 +16575,7 @@
       </c>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="104"/>
+      <c r="D97" s="97"/>
       <c r="E97" s="43" t="s">
         <v>285</v>
       </c>
@@ -16584,7 +16584,7 @@
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="104"/>
+      <c r="D98" s="97"/>
       <c r="E98" s="43" t="s">
         <v>276</v>
       </c>
@@ -16593,7 +16593,7 @@
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="104"/>
+      <c r="D99" s="97"/>
       <c r="E99" s="43" t="s">
         <v>283</v>
       </c>
@@ -16602,7 +16602,7 @@
       </c>
     </row>
     <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="104" t="s">
+      <c r="D100" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E100" s="43" t="s">
@@ -16613,7 +16613,7 @@
       </c>
     </row>
     <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>282</v>
       </c>
@@ -16630,24 +16630,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:K15"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D23:D34"/>
-    <mergeCell ref="D35:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D51:D56"/>
     <mergeCell ref="D100:D101"/>
     <mergeCell ref="D85:D90"/>
     <mergeCell ref="D94:D99"/>
@@ -16656,6 +16638,24 @@
     <mergeCell ref="D69:D70"/>
     <mergeCell ref="D71:D82"/>
     <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:D34"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D51:D56"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:K15"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -16786,52 +16786,52 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D15" s="97" t="s">
+      <c r="D15" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="96" t="s">
+      <c r="E15" s="98"/>
+      <c r="F15" s="99" t="s">
         <v>689</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="100" t="s">
+      <c r="F16" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="100" t="s">
+      <c r="G16" s="103"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="J16" s="101"/>
-      <c r="K16" s="102"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="104"/>
     </row>
     <row r="17" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D17" s="99"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F17" s="105" t="s">
+      <c r="F17" s="106" t="s">
         <v>690</v>
       </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105" t="s">
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106" t="s">
         <v>690</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="21"/>
     </row>
     <row r="18" spans="4:42" x14ac:dyDescent="0.25">
@@ -16841,16 +16841,16 @@
       <c r="E18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105" t="s">
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
       <c r="L18" s="21"/>
     </row>
     <row r="19" spans="4:42" x14ac:dyDescent="0.25">
@@ -16860,16 +16860,16 @@
       <c r="E19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105" t="s">
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
       <c r="L19" s="21"/>
     </row>
     <row r="20" spans="4:42" x14ac:dyDescent="0.25">
@@ -16879,23 +16879,23 @@
       <c r="E20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105" t="s">
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
       <c r="L20" s="21"/>
     </row>
     <row r="21" spans="4:42" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="104"/>
+      <c r="E21" s="97"/>
       <c r="F21" s="50" t="s">
         <v>305</v>
       </c>
@@ -16974,7 +16974,7 @@
       <c r="L22" s="21"/>
     </row>
     <row r="23" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E23" s="42" t="s">
@@ -17007,7 +17007,7 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D24" s="104"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="42" t="s">
         <v>274</v>
       </c>
@@ -17038,7 +17038,7 @@
       <c r="L24" s="21"/>
     </row>
     <row r="25" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D25" s="104"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="42" t="s">
         <v>282</v>
       </c>
@@ -17069,7 +17069,7 @@
       <c r="L25" s="21"/>
     </row>
     <row r="26" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>275</v>
       </c>
@@ -17100,7 +17100,7 @@
       <c r="L26" s="36"/>
     </row>
     <row r="27" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>302</v>
       </c>
@@ -17131,7 +17131,7 @@
       <c r="L27" s="33"/>
     </row>
     <row r="28" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>284</v>
       </c>
@@ -17162,7 +17162,7 @@
       <c r="L28" s="33"/>
     </row>
     <row r="29" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>285</v>
       </c>
@@ -17193,7 +17193,7 @@
       <c r="L29" s="33"/>
     </row>
     <row r="30" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>286</v>
       </c>
@@ -17224,7 +17224,7 @@
       <c r="L30" s="33"/>
     </row>
     <row r="31" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>276</v>
       </c>
@@ -17255,7 +17255,7 @@
       <c r="L31" s="33"/>
     </row>
     <row r="32" spans="4:42" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>277</v>
       </c>
@@ -17286,7 +17286,7 @@
       <c r="L32" s="33"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>283</v>
       </c>
@@ -17317,7 +17317,7 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>278</v>
       </c>
@@ -17348,7 +17348,7 @@
       <c r="L34" s="33"/>
     </row>
     <row r="35" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="104" t="s">
+      <c r="D35" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="42" t="s">
@@ -17379,7 +17379,7 @@
       <c r="L35" s="33"/>
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D36" s="104"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="42" t="s">
         <v>280</v>
       </c>
@@ -17408,7 +17408,7 @@
       <c r="L36" s="38"/>
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D37" s="104"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="42" t="s">
         <v>287</v>
       </c>
@@ -17437,7 +17437,7 @@
       <c r="L37" s="38"/>
     </row>
     <row r="38" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>281</v>
       </c>
@@ -17466,7 +17466,7 @@
       <c r="L38" s="38"/>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>276</v>
       </c>
@@ -17495,7 +17495,7 @@
       <c r="L39" s="38"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>277</v>
       </c>
@@ -17524,7 +17524,7 @@
       <c r="L40" s="38"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>283</v>
       </c>
@@ -17552,7 +17552,7 @@
       </c>
     </row>
     <row r="42" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>278</v>
       </c>
@@ -17580,7 +17580,7 @@
       </c>
     </row>
     <row r="43" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D43" s="104" t="s">
+      <c r="D43" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="42" t="s">
@@ -17612,7 +17612,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D44" s="104"/>
+      <c r="D44" s="97"/>
       <c r="E44" s="42" t="s">
         <v>274</v>
       </c>
@@ -17642,7 +17642,7 @@
       </c>
     </row>
     <row r="45" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D45" s="104"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="42" t="s">
         <v>282</v>
       </c>
@@ -17672,7 +17672,7 @@
       </c>
     </row>
     <row r="46" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>275</v>
       </c>
@@ -17806,7 +17806,7 @@
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E51" s="43" t="s">
@@ -17832,7 +17832,7 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D52" s="104"/>
+      <c r="D52" s="97"/>
       <c r="E52" s="43" t="s">
         <v>282</v>
       </c>
@@ -17856,7 +17856,7 @@
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D53" s="104"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="43" t="s">
         <v>302</v>
       </c>
@@ -17880,7 +17880,7 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D54" s="104"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="43" t="s">
         <v>285</v>
       </c>
@@ -17904,7 +17904,7 @@
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>276</v>
       </c>
@@ -17928,7 +17928,7 @@
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>283</v>
       </c>
@@ -17952,7 +17952,7 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D57" s="104" t="s">
+      <c r="D57" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E57" s="43" t="s">
@@ -17978,7 +17978,7 @@
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D58" s="104"/>
+      <c r="D58" s="97"/>
       <c r="E58" s="43" t="s">
         <v>282</v>
       </c>
@@ -18054,7 +18054,7 @@
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D67" s="104" t="s">
+      <c r="D67" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E67" s="42" t="s">
@@ -18066,7 +18066,7 @@
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D68" s="104"/>
+      <c r="D68" s="97"/>
       <c r="E68" s="42" t="s">
         <v>296</v>
       </c>
@@ -18076,7 +18076,7 @@
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D69" s="104" t="s">
+      <c r="D69" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E69" s="42" t="s">
@@ -18088,7 +18088,7 @@
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D70" s="104"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="42" t="s">
         <v>275</v>
       </c>
@@ -18098,7 +18098,7 @@
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E71" s="42" t="s">
@@ -18111,7 +18111,7 @@
       <c r="H71" s="82"/>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="104"/>
+      <c r="D72" s="97"/>
       <c r="E72" s="42" t="s">
         <v>274</v>
       </c>
@@ -18121,7 +18121,7 @@
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="104"/>
+      <c r="D73" s="97"/>
       <c r="E73" s="42" t="s">
         <v>282</v>
       </c>
@@ -18131,7 +18131,7 @@
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="104"/>
+      <c r="D74" s="97"/>
       <c r="E74" s="42" t="s">
         <v>275</v>
       </c>
@@ -18141,7 +18141,7 @@
       </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>302</v>
       </c>
@@ -18151,7 +18151,7 @@
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="104"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="42" t="s">
         <v>284</v>
       </c>
@@ -18161,7 +18161,7 @@
       </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>285</v>
       </c>
@@ -18171,7 +18171,7 @@
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>286</v>
       </c>
@@ -18181,7 +18181,7 @@
       </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>276</v>
       </c>
@@ -18191,7 +18191,7 @@
       </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>277</v>
       </c>
@@ -18201,7 +18201,7 @@
       </c>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>283</v>
       </c>
@@ -18211,7 +18211,7 @@
       </c>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>278</v>
       </c>
@@ -18221,7 +18221,7 @@
       </c>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="104" t="s">
+      <c r="D83" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E83" s="42" t="s">
@@ -18233,7 +18233,7 @@
       </c>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>287</v>
       </c>
@@ -18243,7 +18243,7 @@
       </c>
     </row>
     <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="104" t="s">
+      <c r="D85" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E85" s="42" t="s">
@@ -18255,7 +18255,7 @@
       </c>
     </row>
     <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>281</v>
       </c>
@@ -18265,7 +18265,7 @@
       </c>
     </row>
     <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="104"/>
+      <c r="D87" s="97"/>
       <c r="E87" s="42" t="s">
         <v>277</v>
       </c>
@@ -18275,7 +18275,7 @@
       </c>
     </row>
     <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="104"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="42" t="s">
         <v>283</v>
       </c>
@@ -18285,7 +18285,7 @@
       </c>
     </row>
     <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>276</v>
       </c>
@@ -18295,7 +18295,7 @@
       </c>
     </row>
     <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="104"/>
+      <c r="D90" s="97"/>
       <c r="E90" s="42" t="s">
         <v>278</v>
       </c>
@@ -18338,7 +18338,7 @@
       </c>
     </row>
     <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="104" t="s">
+      <c r="D94" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E94" s="43" t="s">
@@ -18349,7 +18349,7 @@
       </c>
     </row>
     <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="104"/>
+      <c r="D95" s="97"/>
       <c r="E95" s="43" t="s">
         <v>282</v>
       </c>
@@ -18358,7 +18358,7 @@
       </c>
     </row>
     <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="104"/>
+      <c r="D96" s="97"/>
       <c r="E96" s="43" t="s">
         <v>302</v>
       </c>
@@ -18367,7 +18367,7 @@
       </c>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="104"/>
+      <c r="D97" s="97"/>
       <c r="E97" s="43" t="s">
         <v>285</v>
       </c>
@@ -18376,7 +18376,7 @@
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="104"/>
+      <c r="D98" s="97"/>
       <c r="E98" s="43" t="s">
         <v>276</v>
       </c>
@@ -18385,7 +18385,7 @@
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="104"/>
+      <c r="D99" s="97"/>
       <c r="E99" s="43" t="s">
         <v>283</v>
       </c>
@@ -18394,7 +18394,7 @@
       </c>
     </row>
     <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="104" t="s">
+      <c r="D100" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E100" s="43" t="s">
@@ -18405,7 +18405,7 @@
       </c>
     </row>
     <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>282</v>
       </c>
@@ -18422,6 +18422,17 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D94:D99"/>
+    <mergeCell ref="D71:D82"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="D51:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="D43:D46"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D23:D34"/>
     <mergeCell ref="F19:H19"/>
@@ -18437,17 +18448,6 @@
     <mergeCell ref="I18:K18"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I17:K17"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="D51:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D35:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D94:D99"/>
-    <mergeCell ref="D71:D82"/>
-    <mergeCell ref="D83:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -18568,52 +18568,52 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="97" t="s">
+      <c r="D15" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="96" t="s">
+      <c r="E15" s="98"/>
+      <c r="F15" s="99" t="s">
         <v>689</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="100" t="s">
+      <c r="F16" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="100" t="s">
+      <c r="G16" s="103"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="J16" s="101"/>
-      <c r="K16" s="102"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="104"/>
     </row>
     <row r="17" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D17" s="99"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F17" s="105" t="s">
+      <c r="F17" s="106" t="s">
         <v>689</v>
       </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105" t="s">
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106" t="s">
         <v>689</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="21"/>
     </row>
     <row r="18" spans="4:33" x14ac:dyDescent="0.25">
@@ -18623,16 +18623,16 @@
       <c r="E18" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105" t="s">
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106" t="s">
         <v>691</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
       <c r="L18" s="21"/>
     </row>
     <row r="19" spans="4:33" x14ac:dyDescent="0.25">
@@ -18642,16 +18642,16 @@
       <c r="E19" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105" t="s">
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106" t="s">
         <v>692</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
       <c r="L19" s="21"/>
     </row>
     <row r="20" spans="4:33" x14ac:dyDescent="0.25">
@@ -18661,23 +18661,23 @@
       <c r="E20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105" t="s">
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106" t="s">
         <v>693</v>
       </c>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
       <c r="L20" s="21"/>
     </row>
     <row r="21" spans="4:33" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="104"/>
+      <c r="E21" s="97"/>
       <c r="F21" s="50" t="s">
         <v>305</v>
       </c>
@@ -18747,7 +18747,7 @@
       <c r="L22" s="21"/>
     </row>
     <row r="23" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E23" s="42" t="s">
@@ -18774,7 +18774,7 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D24" s="104"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="42" t="s">
         <v>274</v>
       </c>
@@ -18799,7 +18799,7 @@
       <c r="L24" s="21"/>
     </row>
     <row r="25" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D25" s="104"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="42" t="s">
         <v>282</v>
       </c>
@@ -18824,7 +18824,7 @@
       <c r="L25" s="21"/>
     </row>
     <row r="26" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>275</v>
       </c>
@@ -18849,7 +18849,7 @@
       <c r="L26" s="36"/>
     </row>
     <row r="27" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>302</v>
       </c>
@@ -18874,7 +18874,7 @@
       <c r="L27" s="33"/>
     </row>
     <row r="28" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>284</v>
       </c>
@@ -18899,7 +18899,7 @@
       <c r="L28" s="33"/>
     </row>
     <row r="29" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>285</v>
       </c>
@@ -18924,7 +18924,7 @@
       <c r="L29" s="33"/>
     </row>
     <row r="30" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>286</v>
       </c>
@@ -18949,7 +18949,7 @@
       <c r="L30" s="33"/>
     </row>
     <row r="31" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>276</v>
       </c>
@@ -18974,7 +18974,7 @@
       <c r="L31" s="33"/>
     </row>
     <row r="32" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>277</v>
       </c>
@@ -18999,7 +18999,7 @@
       <c r="L32" s="33"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>283</v>
       </c>
@@ -19024,7 +19024,7 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>278</v>
       </c>
@@ -19049,7 +19049,7 @@
       <c r="L34" s="33"/>
     </row>
     <row r="35" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="104" t="s">
+      <c r="D35" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="42" t="s">
@@ -19078,7 +19078,7 @@
       <c r="L35" s="33"/>
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D36" s="104"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="42" t="s">
         <v>280</v>
       </c>
@@ -19105,7 +19105,7 @@
       <c r="L36" s="38"/>
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D37" s="104"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="42" t="s">
         <v>287</v>
       </c>
@@ -19132,7 +19132,7 @@
       <c r="L37" s="38"/>
     </row>
     <row r="38" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>281</v>
       </c>
@@ -19159,7 +19159,7 @@
       <c r="L38" s="38"/>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>276</v>
       </c>
@@ -19186,7 +19186,7 @@
       <c r="L39" s="38"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>277</v>
       </c>
@@ -19213,7 +19213,7 @@
       <c r="L40" s="38"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>283</v>
       </c>
@@ -19239,7 +19239,7 @@
       </c>
     </row>
     <row r="42" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>278</v>
       </c>
@@ -19265,7 +19265,7 @@
       </c>
     </row>
     <row r="43" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D43" s="104" t="s">
+      <c r="D43" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="42" t="s">
@@ -19291,7 +19291,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D44" s="104"/>
+      <c r="D44" s="97"/>
       <c r="E44" s="42" t="s">
         <v>274</v>
       </c>
@@ -19315,7 +19315,7 @@
       </c>
     </row>
     <row r="45" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D45" s="104"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="42" t="s">
         <v>282</v>
       </c>
@@ -19339,7 +19339,7 @@
       </c>
     </row>
     <row r="46" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>275</v>
       </c>
@@ -19467,7 +19467,7 @@
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E51" s="43" t="s">
@@ -19495,7 +19495,7 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D52" s="104"/>
+      <c r="D52" s="97"/>
       <c r="E52" s="43" t="s">
         <v>282</v>
       </c>
@@ -19521,7 +19521,7 @@
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D53" s="104"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="43" t="s">
         <v>302</v>
       </c>
@@ -19547,7 +19547,7 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D54" s="104"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="43" t="s">
         <v>285</v>
       </c>
@@ -19573,7 +19573,7 @@
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>276</v>
       </c>
@@ -19599,7 +19599,7 @@
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>283</v>
       </c>
@@ -19625,7 +19625,7 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D57" s="104" t="s">
+      <c r="D57" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E57" s="43" t="s">
@@ -19653,7 +19653,7 @@
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D58" s="104"/>
+      <c r="D58" s="97"/>
       <c r="E58" s="43" t="s">
         <v>282</v>
       </c>
@@ -19733,7 +19733,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="104" t="s">
+      <c r="D67" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E67" s="42" t="s">
@@ -19744,7 +19744,7 @@
       </c>
     </row>
     <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="104"/>
+      <c r="D68" s="97"/>
       <c r="E68" s="42" t="s">
         <v>296</v>
       </c>
@@ -19753,7 +19753,7 @@
       </c>
     </row>
     <row r="69" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="104" t="s">
+      <c r="D69" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E69" s="42" t="s">
@@ -19764,7 +19764,7 @@
       </c>
     </row>
     <row r="70" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="104"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="42" t="s">
         <v>275</v>
       </c>
@@ -19773,7 +19773,7 @@
       </c>
     </row>
     <row r="71" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E71" s="42" t="s">
@@ -19784,7 +19784,7 @@
       </c>
     </row>
     <row r="72" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="104"/>
+      <c r="D72" s="97"/>
       <c r="E72" s="42" t="s">
         <v>274</v>
       </c>
@@ -19793,7 +19793,7 @@
       </c>
     </row>
     <row r="73" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D73" s="104"/>
+      <c r="D73" s="97"/>
       <c r="E73" s="42" t="s">
         <v>282</v>
       </c>
@@ -19802,7 +19802,7 @@
       </c>
     </row>
     <row r="74" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D74" s="104"/>
+      <c r="D74" s="97"/>
       <c r="E74" s="42" t="s">
         <v>275</v>
       </c>
@@ -19811,7 +19811,7 @@
       </c>
     </row>
     <row r="75" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>302</v>
       </c>
@@ -19820,7 +19820,7 @@
       </c>
     </row>
     <row r="76" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D76" s="104"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="42" t="s">
         <v>284</v>
       </c>
@@ -19829,7 +19829,7 @@
       </c>
     </row>
     <row r="77" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>285</v>
       </c>
@@ -19838,7 +19838,7 @@
       </c>
     </row>
     <row r="78" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>286</v>
       </c>
@@ -19847,7 +19847,7 @@
       </c>
     </row>
     <row r="79" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>276</v>
       </c>
@@ -19856,7 +19856,7 @@
       </c>
     </row>
     <row r="80" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>277</v>
       </c>
@@ -19865,7 +19865,7 @@
       </c>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>283</v>
       </c>
@@ -19874,7 +19874,7 @@
       </c>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>278</v>
       </c>
@@ -19883,7 +19883,7 @@
       </c>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="104" t="s">
+      <c r="D83" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E83" s="42" t="s">
@@ -19895,7 +19895,7 @@
       </c>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>287</v>
       </c>
@@ -19905,7 +19905,7 @@
       </c>
     </row>
     <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="104" t="s">
+      <c r="D85" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E85" s="42" t="s">
@@ -19917,7 +19917,7 @@
       </c>
     </row>
     <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>281</v>
       </c>
@@ -19927,7 +19927,7 @@
       </c>
     </row>
     <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="104"/>
+      <c r="D87" s="97"/>
       <c r="E87" s="42" t="s">
         <v>277</v>
       </c>
@@ -19937,7 +19937,7 @@
       </c>
     </row>
     <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="104"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="42" t="s">
         <v>283</v>
       </c>
@@ -19947,7 +19947,7 @@
       </c>
     </row>
     <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>276</v>
       </c>
@@ -19957,7 +19957,7 @@
       </c>
     </row>
     <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="104"/>
+      <c r="D90" s="97"/>
       <c r="E90" s="42" t="s">
         <v>278</v>
       </c>
@@ -20000,7 +20000,7 @@
       </c>
     </row>
     <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="104" t="s">
+      <c r="D94" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E94" s="43" t="s">
@@ -20012,7 +20012,7 @@
       </c>
     </row>
     <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="104"/>
+      <c r="D95" s="97"/>
       <c r="E95" s="43" t="s">
         <v>282</v>
       </c>
@@ -20022,7 +20022,7 @@
       </c>
     </row>
     <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="104"/>
+      <c r="D96" s="97"/>
       <c r="E96" s="43" t="s">
         <v>302</v>
       </c>
@@ -20032,7 +20032,7 @@
       </c>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="104"/>
+      <c r="D97" s="97"/>
       <c r="E97" s="43" t="s">
         <v>285</v>
       </c>
@@ -20042,7 +20042,7 @@
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="104"/>
+      <c r="D98" s="97"/>
       <c r="E98" s="43" t="s">
         <v>276</v>
       </c>
@@ -20052,7 +20052,7 @@
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="104"/>
+      <c r="D99" s="97"/>
       <c r="E99" s="43" t="s">
         <v>283</v>
       </c>
@@ -20062,7 +20062,7 @@
       </c>
     </row>
     <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="104" t="s">
+      <c r="D100" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E100" s="43" t="s">
@@ -20074,7 +20074,7 @@
       </c>
     </row>
     <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>282</v>
       </c>
@@ -20092,6 +20092,23 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D94:D99"/>
+    <mergeCell ref="D71:D82"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="D51:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:D34"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:K15"/>
     <mergeCell ref="F17:H17"/>
@@ -20101,23 +20118,6 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="I16:K16"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D23:D34"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="D51:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D35:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D94:D99"/>
-    <mergeCell ref="D71:D82"/>
-    <mergeCell ref="D83:D84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -20259,137 +20259,137 @@
       <c r="C15" s="49"/>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D16" s="97" t="s">
+      <c r="D16" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="96" t="s">
+      <c r="E16" s="98"/>
+      <c r="F16" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="M16" s="97" t="s">
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="M16" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="N16" s="97"/>
-      <c r="O16" s="96" t="s">
+      <c r="N16" s="98"/>
+      <c r="O16" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="96"/>
-      <c r="V16" s="97" t="s">
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="99"/>
+      <c r="V16" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="W16" s="97"/>
-      <c r="X16" s="96" t="s">
+      <c r="W16" s="98"/>
+      <c r="X16" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="Y16" s="96"/>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="96"/>
-      <c r="AB16" s="96"/>
-      <c r="AC16" s="96"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="99"/>
+      <c r="AB16" s="99"/>
+      <c r="AC16" s="99"/>
     </row>
     <row r="17" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D17" s="98" t="s">
+      <c r="D17" s="100" t="s">
         <v>1</v>
       </c>
       <c r="E17" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F17" s="109" t="s">
+      <c r="F17" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="G17" s="110"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="109" t="s">
+      <c r="G17" s="111"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="110" t="s">
         <v>290</v>
       </c>
-      <c r="J17" s="110"/>
-      <c r="K17" s="111"/>
-      <c r="M17" s="98" t="s">
+      <c r="J17" s="111"/>
+      <c r="K17" s="112"/>
+      <c r="M17" s="100" t="s">
         <v>1</v>
       </c>
       <c r="N17" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="O17" s="109" t="s">
+      <c r="O17" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="109" t="s">
+      <c r="P17" s="111"/>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="110" t="s">
         <v>290</v>
       </c>
-      <c r="S17" s="110"/>
-      <c r="T17" s="111"/>
-      <c r="V17" s="98" t="s">
+      <c r="S17" s="111"/>
+      <c r="T17" s="112"/>
+      <c r="V17" s="100" t="s">
         <v>1</v>
       </c>
       <c r="W17" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="X17" s="109" t="s">
+      <c r="X17" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="Y17" s="110"/>
-      <c r="Z17" s="111"/>
-      <c r="AA17" s="109" t="s">
+      <c r="Y17" s="111"/>
+      <c r="Z17" s="112"/>
+      <c r="AA17" s="110" t="s">
         <v>290</v>
       </c>
-      <c r="AB17" s="110"/>
-      <c r="AC17" s="111"/>
+      <c r="AB17" s="111"/>
+      <c r="AC17" s="112"/>
     </row>
     <row r="18" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D18" s="99"/>
+      <c r="D18" s="101"/>
       <c r="E18" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F18" s="103" t="s">
+      <c r="F18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103" t="s">
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="99"/>
+      <c r="M18" s="101"/>
       <c r="N18" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="O18" s="103" t="s">
+      <c r="O18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103" t="s">
+      <c r="P18" s="105"/>
+      <c r="Q18" s="105"/>
+      <c r="R18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="V18" s="99"/>
+      <c r="S18" s="105"/>
+      <c r="T18" s="105"/>
+      <c r="V18" s="101"/>
       <c r="W18" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X18" s="103" t="s">
+      <c r="X18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="Y18" s="103"/>
-      <c r="Z18" s="103"/>
-      <c r="AA18" s="103" t="s">
+      <c r="Y18" s="105"/>
+      <c r="Z18" s="105"/>
+      <c r="AA18" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AB18" s="103"/>
-      <c r="AC18" s="103"/>
+      <c r="AB18" s="105"/>
+      <c r="AC18" s="105"/>
     </row>
     <row r="19" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D19" s="47" t="s">
@@ -20398,16 +20398,16 @@
       <c r="E19" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="F19" s="103" t="s">
+      <c r="F19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103" t="s">
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
       <c r="L19" s="21"/>
       <c r="M19" s="47" t="s">
         <v>265</v>
@@ -20415,32 +20415,32 @@
       <c r="N19" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="O19" s="103" t="s">
+      <c r="O19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="P19" s="103"/>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103" t="s">
+      <c r="P19" s="105"/>
+      <c r="Q19" s="105"/>
+      <c r="R19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="S19" s="103"/>
-      <c r="T19" s="103"/>
+      <c r="S19" s="105"/>
+      <c r="T19" s="105"/>
       <c r="V19" s="47" t="s">
         <v>265</v>
       </c>
       <c r="W19" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="X19" s="103" t="s">
+      <c r="X19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="Y19" s="103"/>
-      <c r="Z19" s="103"/>
-      <c r="AA19" s="103" t="s">
+      <c r="Y19" s="105"/>
+      <c r="Z19" s="105"/>
+      <c r="AA19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AB19" s="103"/>
-      <c r="AC19" s="103"/>
+      <c r="AB19" s="105"/>
+      <c r="AC19" s="105"/>
     </row>
     <row r="20" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D20" s="47" t="s">
@@ -20449,16 +20449,16 @@
       <c r="E20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="F20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103" t="s">
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
       <c r="L20" s="21"/>
       <c r="M20" s="47" t="s">
         <v>266</v>
@@ -20466,32 +20466,32 @@
       <c r="N20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="O20" s="103" t="s">
+      <c r="O20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="P20" s="103"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="103" t="s">
+      <c r="P20" s="105"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="S20" s="103"/>
-      <c r="T20" s="103"/>
+      <c r="S20" s="105"/>
+      <c r="T20" s="105"/>
       <c r="V20" s="47" t="s">
         <v>266</v>
       </c>
       <c r="W20" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X20" s="103" t="s">
+      <c r="X20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="Y20" s="103"/>
-      <c r="Z20" s="103"/>
-      <c r="AA20" s="103" t="s">
+      <c r="Y20" s="105"/>
+      <c r="Z20" s="105"/>
+      <c r="AA20" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AB20" s="103"/>
-      <c r="AC20" s="103"/>
+      <c r="AB20" s="105"/>
+      <c r="AC20" s="105"/>
     </row>
     <row r="21" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D21" s="47" t="s">
@@ -20500,16 +20500,16 @@
       <c r="E21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F21" s="103" t="s">
+      <c r="F21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103" t="s">
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
       <c r="L21" s="21"/>
       <c r="M21" s="47" t="s">
         <v>267</v>
@@ -20517,38 +20517,38 @@
       <c r="N21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="O21" s="103" t="s">
+      <c r="O21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="P21" s="103"/>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="103" t="s">
+      <c r="P21" s="105"/>
+      <c r="Q21" s="105"/>
+      <c r="R21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="103"/>
-      <c r="T21" s="103"/>
+      <c r="S21" s="105"/>
+      <c r="T21" s="105"/>
       <c r="V21" s="47" t="s">
         <v>267</v>
       </c>
       <c r="W21" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="X21" s="103" t="s">
+      <c r="X21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="Y21" s="103"/>
-      <c r="Z21" s="103"/>
-      <c r="AA21" s="103" t="s">
+      <c r="Y21" s="105"/>
+      <c r="Z21" s="105"/>
+      <c r="AA21" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AB21" s="103"/>
-      <c r="AC21" s="103"/>
+      <c r="AB21" s="105"/>
+      <c r="AC21" s="105"/>
     </row>
     <row r="22" spans="4:29" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="D22" s="104" t="s">
+      <c r="D22" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="104"/>
+      <c r="E22" s="97"/>
       <c r="F22" s="50" t="s">
         <v>305</v>
       </c>
@@ -20568,10 +20568,10 @@
         <v>10</v>
       </c>
       <c r="L22" s="21"/>
-      <c r="M22" s="104" t="s">
+      <c r="M22" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="N22" s="104"/>
+      <c r="N22" s="97"/>
       <c r="O22" s="50" t="s">
         <v>305</v>
       </c>
@@ -20590,10 +20590,10 @@
       <c r="T22" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="104" t="s">
+      <c r="V22" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="W22" s="104"/>
+      <c r="W22" s="97"/>
       <c r="X22" s="50" t="s">
         <v>305</v>
       </c>
@@ -20689,7 +20689,7 @@
       </c>
     </row>
     <row r="24" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D24" s="104" t="s">
+      <c r="D24" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E24" s="42" t="s">
@@ -20714,7 +20714,7 @@
         <v>11</v>
       </c>
       <c r="L24" s="21"/>
-      <c r="M24" s="104" t="s">
+      <c r="M24" s="97" t="s">
         <v>269</v>
       </c>
       <c r="N24" s="42" t="s">
@@ -20738,7 +20738,7 @@
       <c r="T24" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V24" s="104" t="s">
+      <c r="V24" s="97" t="s">
         <v>269</v>
       </c>
       <c r="W24" s="42" t="s">
@@ -20764,7 +20764,7 @@
       </c>
     </row>
     <row r="25" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D25" s="104"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="42" t="s">
         <v>274</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>11</v>
       </c>
       <c r="L25" s="21"/>
-      <c r="M25" s="104"/>
+      <c r="M25" s="97"/>
       <c r="N25" s="42" t="s">
         <v>274</v>
       </c>
@@ -20809,7 +20809,7 @@
       <c r="T25" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V25" s="104"/>
+      <c r="V25" s="97"/>
       <c r="W25" s="42" t="s">
         <v>274</v>
       </c>
@@ -20833,7 +20833,7 @@
       </c>
     </row>
     <row r="26" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D26" s="104"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="42" t="s">
         <v>282</v>
       </c>
@@ -20856,7 +20856,7 @@
         <v>11</v>
       </c>
       <c r="L26" s="21"/>
-      <c r="M26" s="104"/>
+      <c r="M26" s="97"/>
       <c r="N26" s="42" t="s">
         <v>282</v>
       </c>
@@ -20878,7 +20878,7 @@
       <c r="T26" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V26" s="104"/>
+      <c r="V26" s="97"/>
       <c r="W26" s="42" t="s">
         <v>282</v>
       </c>
@@ -20902,7 +20902,7 @@
       </c>
     </row>
     <row r="27" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D27" s="104"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="42" t="s">
         <v>275</v>
       </c>
@@ -20925,7 +20925,7 @@
         <v>11</v>
       </c>
       <c r="L27" s="36"/>
-      <c r="M27" s="104"/>
+      <c r="M27" s="97"/>
       <c r="N27" s="42" t="s">
         <v>275</v>
       </c>
@@ -20947,7 +20947,7 @@
       <c r="T27" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V27" s="104"/>
+      <c r="V27" s="97"/>
       <c r="W27" s="42" t="s">
         <v>275</v>
       </c>
@@ -20971,7 +20971,7 @@
       </c>
     </row>
     <row r="28" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D28" s="104"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="42" t="s">
         <v>302</v>
       </c>
@@ -20994,7 +20994,7 @@
         <v>11</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="104"/>
+      <c r="M28" s="97"/>
       <c r="N28" s="42" t="s">
         <v>302</v>
       </c>
@@ -21016,7 +21016,7 @@
       <c r="T28" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V28" s="104"/>
+      <c r="V28" s="97"/>
       <c r="W28" s="42" t="s">
         <v>302</v>
       </c>
@@ -21040,7 +21040,7 @@
       </c>
     </row>
     <row r="29" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D29" s="104"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="42" t="s">
         <v>284</v>
       </c>
@@ -21063,7 +21063,7 @@
         <v>11</v>
       </c>
       <c r="L29" s="33"/>
-      <c r="M29" s="104"/>
+      <c r="M29" s="97"/>
       <c r="N29" s="42" t="s">
         <v>284</v>
       </c>
@@ -21085,7 +21085,7 @@
       <c r="T29" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V29" s="104"/>
+      <c r="V29" s="97"/>
       <c r="W29" s="42" t="s">
         <v>284</v>
       </c>
@@ -21109,7 +21109,7 @@
       </c>
     </row>
     <row r="30" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D30" s="104"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="42" t="s">
         <v>285</v>
       </c>
@@ -21132,7 +21132,7 @@
         <v>11</v>
       </c>
       <c r="L30" s="33"/>
-      <c r="M30" s="104"/>
+      <c r="M30" s="97"/>
       <c r="N30" s="42" t="s">
         <v>285</v>
       </c>
@@ -21154,7 +21154,7 @@
       <c r="T30" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V30" s="104"/>
+      <c r="V30" s="97"/>
       <c r="W30" s="42" t="s">
         <v>285</v>
       </c>
@@ -21178,7 +21178,7 @@
       </c>
     </row>
     <row r="31" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D31" s="104"/>
+      <c r="D31" s="97"/>
       <c r="E31" s="42" t="s">
         <v>286</v>
       </c>
@@ -21201,7 +21201,7 @@
         <v>11</v>
       </c>
       <c r="L31" s="33"/>
-      <c r="M31" s="104"/>
+      <c r="M31" s="97"/>
       <c r="N31" s="42" t="s">
         <v>286</v>
       </c>
@@ -21223,7 +21223,7 @@
       <c r="T31" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V31" s="104"/>
+      <c r="V31" s="97"/>
       <c r="W31" s="42" t="s">
         <v>286</v>
       </c>
@@ -21247,7 +21247,7 @@
       </c>
     </row>
     <row r="32" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D32" s="104"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="42" t="s">
         <v>276</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>11</v>
       </c>
       <c r="L32" s="33"/>
-      <c r="M32" s="104"/>
+      <c r="M32" s="97"/>
       <c r="N32" s="42" t="s">
         <v>276</v>
       </c>
@@ -21292,7 +21292,7 @@
       <c r="T32" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V32" s="104"/>
+      <c r="V32" s="97"/>
       <c r="W32" s="42" t="s">
         <v>276</v>
       </c>
@@ -21316,7 +21316,7 @@
       </c>
     </row>
     <row r="33" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D33" s="104"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="42" t="s">
         <v>277</v>
       </c>
@@ -21339,7 +21339,7 @@
         <v>11</v>
       </c>
       <c r="L33" s="33"/>
-      <c r="M33" s="104"/>
+      <c r="M33" s="97"/>
       <c r="N33" s="42" t="s">
         <v>277</v>
       </c>
@@ -21361,7 +21361,7 @@
       <c r="T33" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V33" s="104"/>
+      <c r="V33" s="97"/>
       <c r="W33" s="42" t="s">
         <v>277</v>
       </c>
@@ -21385,7 +21385,7 @@
       </c>
     </row>
     <row r="34" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D34" s="104"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="42" t="s">
         <v>283</v>
       </c>
@@ -21408,7 +21408,7 @@
         <v>11</v>
       </c>
       <c r="L34" s="33"/>
-      <c r="M34" s="104"/>
+      <c r="M34" s="97"/>
       <c r="N34" s="42" t="s">
         <v>283</v>
       </c>
@@ -21430,7 +21430,7 @@
       <c r="T34" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V34" s="104"/>
+      <c r="V34" s="97"/>
       <c r="W34" s="42" t="s">
         <v>283</v>
       </c>
@@ -21454,7 +21454,7 @@
       </c>
     </row>
     <row r="35" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D35" s="104"/>
+      <c r="D35" s="97"/>
       <c r="E35" s="42" t="s">
         <v>278</v>
       </c>
@@ -21477,7 +21477,7 @@
         <v>11</v>
       </c>
       <c r="L35" s="33"/>
-      <c r="M35" s="104"/>
+      <c r="M35" s="97"/>
       <c r="N35" s="42" t="s">
         <v>278</v>
       </c>
@@ -21499,7 +21499,7 @@
       <c r="T35" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V35" s="104"/>
+      <c r="V35" s="97"/>
       <c r="W35" s="42" t="s">
         <v>278</v>
       </c>
@@ -21523,7 +21523,7 @@
       </c>
     </row>
     <row r="36" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D36" s="104" t="s">
+      <c r="D36" s="97" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="42" t="s">
@@ -21548,7 +21548,7 @@
         <v>9</v>
       </c>
       <c r="L36" s="33"/>
-      <c r="M36" s="104" t="s">
+      <c r="M36" s="97" t="s">
         <v>4</v>
       </c>
       <c r="N36" s="42" t="s">
@@ -21572,7 +21572,7 @@
       <c r="T36" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V36" s="104" t="s">
+      <c r="V36" s="97" t="s">
         <v>4</v>
       </c>
       <c r="W36" s="42" t="s">
@@ -21598,7 +21598,7 @@
       </c>
     </row>
     <row r="37" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D37" s="104"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="42" t="s">
         <v>280</v>
       </c>
@@ -21621,7 +21621,7 @@
         <v>9</v>
       </c>
       <c r="L37" s="38"/>
-      <c r="M37" s="104"/>
+      <c r="M37" s="97"/>
       <c r="N37" s="42" t="s">
         <v>280</v>
       </c>
@@ -21643,7 +21643,7 @@
       <c r="T37" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V37" s="104"/>
+      <c r="V37" s="97"/>
       <c r="W37" s="42" t="s">
         <v>280</v>
       </c>
@@ -21667,7 +21667,7 @@
       </c>
     </row>
     <row r="38" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D38" s="104"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="42" t="s">
         <v>287</v>
       </c>
@@ -21690,7 +21690,7 @@
         <v>9</v>
       </c>
       <c r="L38" s="38"/>
-      <c r="M38" s="104"/>
+      <c r="M38" s="97"/>
       <c r="N38" s="42" t="s">
         <v>287</v>
       </c>
@@ -21712,7 +21712,7 @@
       <c r="T38" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V38" s="104"/>
+      <c r="V38" s="97"/>
       <c r="W38" s="42" t="s">
         <v>287</v>
       </c>
@@ -21736,7 +21736,7 @@
       </c>
     </row>
     <row r="39" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D39" s="104"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="42" t="s">
         <v>281</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>9</v>
       </c>
       <c r="L39" s="38"/>
-      <c r="M39" s="104"/>
+      <c r="M39" s="97"/>
       <c r="N39" s="42" t="s">
         <v>281</v>
       </c>
@@ -21781,7 +21781,7 @@
       <c r="T39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V39" s="104"/>
+      <c r="V39" s="97"/>
       <c r="W39" s="42" t="s">
         <v>281</v>
       </c>
@@ -21805,7 +21805,7 @@
       </c>
     </row>
     <row r="40" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D40" s="104"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="42" t="s">
         <v>276</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>9</v>
       </c>
       <c r="L40" s="38"/>
-      <c r="M40" s="104"/>
+      <c r="M40" s="97"/>
       <c r="N40" s="42" t="s">
         <v>276</v>
       </c>
@@ -21850,7 +21850,7 @@
       <c r="T40" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V40" s="104"/>
+      <c r="V40" s="97"/>
       <c r="W40" s="42" t="s">
         <v>276</v>
       </c>
@@ -21874,7 +21874,7 @@
       </c>
     </row>
     <row r="41" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D41" s="104"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="42" t="s">
         <v>277</v>
       </c>
@@ -21897,7 +21897,7 @@
         <v>9</v>
       </c>
       <c r="L41" s="38"/>
-      <c r="M41" s="104"/>
+      <c r="M41" s="97"/>
       <c r="N41" s="42" t="s">
         <v>277</v>
       </c>
@@ -21919,7 +21919,7 @@
       <c r="T41" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V41" s="104"/>
+      <c r="V41" s="97"/>
       <c r="W41" s="42" t="s">
         <v>277</v>
       </c>
@@ -21943,7 +21943,7 @@
       </c>
     </row>
     <row r="42" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D42" s="104"/>
+      <c r="D42" s="97"/>
       <c r="E42" s="42" t="s">
         <v>283</v>
       </c>
@@ -21965,7 +21965,7 @@
       <c r="K42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M42" s="104"/>
+      <c r="M42" s="97"/>
       <c r="N42" s="42" t="s">
         <v>283</v>
       </c>
@@ -21987,7 +21987,7 @@
       <c r="T42" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V42" s="104"/>
+      <c r="V42" s="97"/>
       <c r="W42" s="42" t="s">
         <v>283</v>
       </c>
@@ -22011,7 +22011,7 @@
       </c>
     </row>
     <row r="43" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D43" s="104"/>
+      <c r="D43" s="97"/>
       <c r="E43" s="42" t="s">
         <v>278</v>
       </c>
@@ -22033,7 +22033,7 @@
       <c r="K43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M43" s="104"/>
+      <c r="M43" s="97"/>
       <c r="N43" s="42" t="s">
         <v>278</v>
       </c>
@@ -22055,7 +22055,7 @@
       <c r="T43" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V43" s="104"/>
+      <c r="V43" s="97"/>
       <c r="W43" s="42" t="s">
         <v>278</v>
       </c>
@@ -22079,7 +22079,7 @@
       </c>
     </row>
     <row r="44" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D44" s="104" t="s">
+      <c r="D44" s="97" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="42" t="s">
@@ -22103,7 +22103,7 @@
       <c r="K44" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M44" s="104" t="s">
+      <c r="M44" s="97" t="s">
         <v>3</v>
       </c>
       <c r="N44" s="42" t="s">
@@ -22127,7 +22127,7 @@
       <c r="T44" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V44" s="104" t="s">
+      <c r="V44" s="97" t="s">
         <v>3</v>
       </c>
       <c r="W44" s="42" t="s">
@@ -22153,7 +22153,7 @@
       </c>
     </row>
     <row r="45" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D45" s="104"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="42" t="s">
         <v>274</v>
       </c>
@@ -22175,7 +22175,7 @@
       <c r="K45" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M45" s="104"/>
+      <c r="M45" s="97"/>
       <c r="N45" s="42" t="s">
         <v>274</v>
       </c>
@@ -22197,7 +22197,7 @@
       <c r="T45" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V45" s="104"/>
+      <c r="V45" s="97"/>
       <c r="W45" s="42" t="s">
         <v>274</v>
       </c>
@@ -22221,7 +22221,7 @@
       </c>
     </row>
     <row r="46" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D46" s="104"/>
+      <c r="D46" s="97"/>
       <c r="E46" s="42" t="s">
         <v>282</v>
       </c>
@@ -22243,7 +22243,7 @@
       <c r="K46" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M46" s="104"/>
+      <c r="M46" s="97"/>
       <c r="N46" s="42" t="s">
         <v>282</v>
       </c>
@@ -22265,7 +22265,7 @@
       <c r="T46" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V46" s="104"/>
+      <c r="V46" s="97"/>
       <c r="W46" s="42" t="s">
         <v>282</v>
       </c>
@@ -22289,7 +22289,7 @@
       </c>
     </row>
     <row r="47" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D47" s="104"/>
+      <c r="D47" s="97"/>
       <c r="E47" s="42" t="s">
         <v>275</v>
       </c>
@@ -22311,7 +22311,7 @@
       <c r="K47" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="104"/>
+      <c r="M47" s="97"/>
       <c r="N47" s="42" t="s">
         <v>275</v>
       </c>
@@ -22333,7 +22333,7 @@
       <c r="T47" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="V47" s="104"/>
+      <c r="V47" s="97"/>
       <c r="W47" s="42" t="s">
         <v>275</v>
       </c>
@@ -22653,7 +22653,7 @@
       </c>
     </row>
     <row r="52" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D52" s="104" t="s">
+      <c r="D52" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E52" s="43" t="s">
@@ -22677,7 +22677,7 @@
       <c r="K52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M52" s="104" t="s">
+      <c r="M52" s="97" t="s">
         <v>300</v>
       </c>
       <c r="N52" s="43" t="s">
@@ -22701,7 +22701,7 @@
       <c r="T52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V52" s="104" t="s">
+      <c r="V52" s="97" t="s">
         <v>300</v>
       </c>
       <c r="W52" s="43" t="s">
@@ -22727,7 +22727,7 @@
       </c>
     </row>
     <row r="53" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D53" s="104"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="43" t="s">
         <v>282</v>
       </c>
@@ -22749,7 +22749,7 @@
       <c r="K53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M53" s="104"/>
+      <c r="M53" s="97"/>
       <c r="N53" s="43" t="s">
         <v>282</v>
       </c>
@@ -22771,7 +22771,7 @@
       <c r="T53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V53" s="104"/>
+      <c r="V53" s="97"/>
       <c r="W53" s="43" t="s">
         <v>282</v>
       </c>
@@ -22795,7 +22795,7 @@
       </c>
     </row>
     <row r="54" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D54" s="104"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="43" t="s">
         <v>302</v>
       </c>
@@ -22817,7 +22817,7 @@
       <c r="K54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M54" s="104"/>
+      <c r="M54" s="97"/>
       <c r="N54" s="43" t="s">
         <v>302</v>
       </c>
@@ -22839,7 +22839,7 @@
       <c r="T54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V54" s="104"/>
+      <c r="V54" s="97"/>
       <c r="W54" s="43" t="s">
         <v>302</v>
       </c>
@@ -22863,7 +22863,7 @@
       </c>
     </row>
     <row r="55" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D55" s="104"/>
+      <c r="D55" s="97"/>
       <c r="E55" s="43" t="s">
         <v>285</v>
       </c>
@@ -22885,7 +22885,7 @@
       <c r="K55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M55" s="104"/>
+      <c r="M55" s="97"/>
       <c r="N55" s="43" t="s">
         <v>285</v>
       </c>
@@ -22907,7 +22907,7 @@
       <c r="T55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V55" s="104"/>
+      <c r="V55" s="97"/>
       <c r="W55" s="43" t="s">
         <v>285</v>
       </c>
@@ -22931,7 +22931,7 @@
       </c>
     </row>
     <row r="56" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D56" s="104"/>
+      <c r="D56" s="97"/>
       <c r="E56" s="43" t="s">
         <v>276</v>
       </c>
@@ -22953,7 +22953,7 @@
       <c r="K56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M56" s="104"/>
+      <c r="M56" s="97"/>
       <c r="N56" s="43" t="s">
         <v>276</v>
       </c>
@@ -22975,7 +22975,7 @@
       <c r="T56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V56" s="104"/>
+      <c r="V56" s="97"/>
       <c r="W56" s="43" t="s">
         <v>276</v>
       </c>
@@ -22999,7 +22999,7 @@
       </c>
     </row>
     <row r="57" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D57" s="104"/>
+      <c r="D57" s="97"/>
       <c r="E57" s="43" t="s">
         <v>283</v>
       </c>
@@ -23021,7 +23021,7 @@
       <c r="K57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M57" s="104"/>
+      <c r="M57" s="97"/>
       <c r="N57" s="43" t="s">
         <v>283</v>
       </c>
@@ -23043,7 +23043,7 @@
       <c r="T57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V57" s="104"/>
+      <c r="V57" s="97"/>
       <c r="W57" s="43" t="s">
         <v>283</v>
       </c>
@@ -23067,7 +23067,7 @@
       </c>
     </row>
     <row r="58" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D58" s="104" t="s">
+      <c r="D58" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E58" s="43" t="s">
@@ -23091,7 +23091,7 @@
       <c r="K58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M58" s="104" t="s">
+      <c r="M58" s="97" t="s">
         <v>301</v>
       </c>
       <c r="N58" s="43" t="s">
@@ -23115,7 +23115,7 @@
       <c r="T58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V58" s="104" t="s">
+      <c r="V58" s="97" t="s">
         <v>301</v>
       </c>
       <c r="W58" s="43" t="s">
@@ -23141,7 +23141,7 @@
       </c>
     </row>
     <row r="59" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D59" s="104"/>
+      <c r="D59" s="97"/>
       <c r="E59" s="43" t="s">
         <v>282</v>
       </c>
@@ -23163,7 +23163,7 @@
       <c r="K59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M59" s="104"/>
+      <c r="M59" s="97"/>
       <c r="N59" s="43" t="s">
         <v>282</v>
       </c>
@@ -23185,7 +23185,7 @@
       <c r="T59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V59" s="104"/>
+      <c r="V59" s="97"/>
       <c r="W59" s="43" t="s">
         <v>282</v>
       </c>
@@ -23322,7 +23322,7 @@
       </c>
     </row>
     <row r="69" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D69" s="104" t="s">
+      <c r="D69" s="97" t="s">
         <v>295</v>
       </c>
       <c r="E69" s="42" t="s">
@@ -23331,7 +23331,7 @@
       <c r="F69" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="104" t="s">
+      <c r="M69" s="97" t="s">
         <v>295</v>
       </c>
       <c r="N69" s="42" t="s">
@@ -23340,7 +23340,7 @@
       <c r="O69" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V69" s="104" t="s">
+      <c r="V69" s="97" t="s">
         <v>295</v>
       </c>
       <c r="W69" s="42" t="s">
@@ -23351,21 +23351,21 @@
       </c>
     </row>
     <row r="70" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D70" s="104"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="42" t="s">
         <v>296</v>
       </c>
       <c r="F70" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M70" s="104"/>
+      <c r="M70" s="97"/>
       <c r="N70" s="42" t="s">
         <v>296</v>
       </c>
       <c r="O70" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V70" s="104"/>
+      <c r="V70" s="97"/>
       <c r="W70" s="42" t="s">
         <v>296</v>
       </c>
@@ -23374,7 +23374,7 @@
       </c>
     </row>
     <row r="71" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D71" s="104" t="s">
+      <c r="D71" s="97" t="s">
         <v>297</v>
       </c>
       <c r="E71" s="42" t="s">
@@ -23383,7 +23383,7 @@
       <c r="F71" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M71" s="104" t="s">
+      <c r="M71" s="97" t="s">
         <v>297</v>
       </c>
       <c r="N71" s="42" t="s">
@@ -23392,7 +23392,7 @@
       <c r="O71" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V71" s="104" t="s">
+      <c r="V71" s="97" t="s">
         <v>297</v>
       </c>
       <c r="W71" s="42" t="s">
@@ -23403,21 +23403,21 @@
       </c>
     </row>
     <row r="72" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D72" s="104"/>
+      <c r="D72" s="97"/>
       <c r="E72" s="42" t="s">
         <v>275</v>
       </c>
       <c r="F72" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="104"/>
+      <c r="M72" s="97"/>
       <c r="N72" s="42" t="s">
         <v>275</v>
       </c>
       <c r="O72" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V72" s="104"/>
+      <c r="V72" s="97"/>
       <c r="W72" s="42" t="s">
         <v>275</v>
       </c>
@@ -23426,7 +23426,7 @@
       </c>
     </row>
     <row r="73" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D73" s="104" t="s">
+      <c r="D73" s="97" t="s">
         <v>269</v>
       </c>
       <c r="E73" s="42" t="s">
@@ -23435,7 +23435,7 @@
       <c r="F73" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M73" s="104" t="s">
+      <c r="M73" s="97" t="s">
         <v>269</v>
       </c>
       <c r="N73" s="42" t="s">
@@ -23444,7 +23444,7 @@
       <c r="O73" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V73" s="104" t="s">
+      <c r="V73" s="97" t="s">
         <v>269</v>
       </c>
       <c r="W73" s="42" t="s">
@@ -23455,21 +23455,21 @@
       </c>
     </row>
     <row r="74" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D74" s="104"/>
+      <c r="D74" s="97"/>
       <c r="E74" s="42" t="s">
         <v>274</v>
       </c>
       <c r="F74" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M74" s="104"/>
+      <c r="M74" s="97"/>
       <c r="N74" s="42" t="s">
         <v>274</v>
       </c>
       <c r="O74" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V74" s="104"/>
+      <c r="V74" s="97"/>
       <c r="W74" s="42" t="s">
         <v>274</v>
       </c>
@@ -23478,21 +23478,21 @@
       </c>
     </row>
     <row r="75" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D75" s="104"/>
+      <c r="D75" s="97"/>
       <c r="E75" s="42" t="s">
         <v>282</v>
       </c>
       <c r="F75" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M75" s="104"/>
+      <c r="M75" s="97"/>
       <c r="N75" s="42" t="s">
         <v>282</v>
       </c>
       <c r="O75" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V75" s="104"/>
+      <c r="V75" s="97"/>
       <c r="W75" s="42" t="s">
         <v>282</v>
       </c>
@@ -23501,21 +23501,21 @@
       </c>
     </row>
     <row r="76" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D76" s="104"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="42" t="s">
         <v>275</v>
       </c>
       <c r="F76" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M76" s="104"/>
+      <c r="M76" s="97"/>
       <c r="N76" s="42" t="s">
         <v>275</v>
       </c>
       <c r="O76" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V76" s="104"/>
+      <c r="V76" s="97"/>
       <c r="W76" s="42" t="s">
         <v>275</v>
       </c>
@@ -23524,21 +23524,21 @@
       </c>
     </row>
     <row r="77" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D77" s="104"/>
+      <c r="D77" s="97"/>
       <c r="E77" s="42" t="s">
         <v>302</v>
       </c>
       <c r="F77" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="104"/>
+      <c r="M77" s="97"/>
       <c r="N77" s="42" t="s">
         <v>302</v>
       </c>
       <c r="O77" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V77" s="104"/>
+      <c r="V77" s="97"/>
       <c r="W77" s="42" t="s">
         <v>302</v>
       </c>
@@ -23547,21 +23547,21 @@
       </c>
     </row>
     <row r="78" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D78" s="104"/>
+      <c r="D78" s="97"/>
       <c r="E78" s="42" t="s">
         <v>284</v>
       </c>
       <c r="F78" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M78" s="104"/>
+      <c r="M78" s="97"/>
       <c r="N78" s="42" t="s">
         <v>284</v>
       </c>
       <c r="O78" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V78" s="104"/>
+      <c r="V78" s="97"/>
       <c r="W78" s="42" t="s">
         <v>284</v>
       </c>
@@ -23570,21 +23570,21 @@
       </c>
     </row>
     <row r="79" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D79" s="104"/>
+      <c r="D79" s="97"/>
       <c r="E79" s="42" t="s">
         <v>285</v>
       </c>
       <c r="F79" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M79" s="104"/>
+      <c r="M79" s="97"/>
       <c r="N79" s="42" t="s">
         <v>285</v>
       </c>
       <c r="O79" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V79" s="104"/>
+      <c r="V79" s="97"/>
       <c r="W79" s="42" t="s">
         <v>285</v>
       </c>
@@ -23593,21 +23593,21 @@
       </c>
     </row>
     <row r="80" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="D80" s="104"/>
+      <c r="D80" s="97"/>
       <c r="E80" s="42" t="s">
         <v>286</v>
       </c>
       <c r="F80" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="104"/>
+      <c r="M80" s="97"/>
       <c r="N80" s="42" t="s">
         <v>286</v>
       </c>
       <c r="O80" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V80" s="104"/>
+      <c r="V80" s="97"/>
       <c r="W80" s="42" t="s">
         <v>286</v>
       </c>
@@ -23616,21 +23616,21 @@
       </c>
     </row>
     <row r="81" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D81" s="104"/>
+      <c r="D81" s="97"/>
       <c r="E81" s="42" t="s">
         <v>276</v>
       </c>
       <c r="F81" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M81" s="104"/>
+      <c r="M81" s="97"/>
       <c r="N81" s="42" t="s">
         <v>276</v>
       </c>
       <c r="O81" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V81" s="104"/>
+      <c r="V81" s="97"/>
       <c r="W81" s="42" t="s">
         <v>276</v>
       </c>
@@ -23639,21 +23639,21 @@
       </c>
     </row>
     <row r="82" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D82" s="104"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="42" t="s">
         <v>277</v>
       </c>
       <c r="F82" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="104"/>
+      <c r="M82" s="97"/>
       <c r="N82" s="42" t="s">
         <v>277</v>
       </c>
       <c r="O82" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V82" s="104"/>
+      <c r="V82" s="97"/>
       <c r="W82" s="42" t="s">
         <v>277</v>
       </c>
@@ -23662,21 +23662,21 @@
       </c>
     </row>
     <row r="83" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D83" s="104"/>
+      <c r="D83" s="97"/>
       <c r="E83" s="42" t="s">
         <v>283</v>
       </c>
       <c r="F83" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M83" s="104"/>
+      <c r="M83" s="97"/>
       <c r="N83" s="42" t="s">
         <v>283</v>
       </c>
       <c r="O83" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V83" s="104"/>
+      <c r="V83" s="97"/>
       <c r="W83" s="42" t="s">
         <v>283</v>
       </c>
@@ -23685,21 +23685,21 @@
       </c>
     </row>
     <row r="84" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D84" s="104"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="42" t="s">
         <v>278</v>
       </c>
       <c r="F84" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M84" s="104"/>
+      <c r="M84" s="97"/>
       <c r="N84" s="42" t="s">
         <v>278</v>
       </c>
       <c r="O84" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V84" s="104"/>
+      <c r="V84" s="97"/>
       <c r="W84" s="42" t="s">
         <v>278</v>
       </c>
@@ -23708,7 +23708,7 @@
       </c>
     </row>
     <row r="85" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D85" s="104" t="s">
+      <c r="D85" s="97" t="s">
         <v>298</v>
       </c>
       <c r="E85" s="42" t="s">
@@ -23717,7 +23717,7 @@
       <c r="F85" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M85" s="104" t="s">
+      <c r="M85" s="97" t="s">
         <v>298</v>
       </c>
       <c r="N85" s="42" t="s">
@@ -23726,7 +23726,7 @@
       <c r="O85" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V85" s="104" t="s">
+      <c r="V85" s="97" t="s">
         <v>298</v>
       </c>
       <c r="W85" s="42" t="s">
@@ -23737,21 +23737,21 @@
       </c>
     </row>
     <row r="86" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D86" s="104"/>
+      <c r="D86" s="97"/>
       <c r="E86" s="42" t="s">
         <v>287</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M86" s="104"/>
+      <c r="M86" s="97"/>
       <c r="N86" s="42" t="s">
         <v>287</v>
       </c>
       <c r="O86" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V86" s="104"/>
+      <c r="V86" s="97"/>
       <c r="W86" s="42" t="s">
         <v>287</v>
       </c>
@@ -23760,7 +23760,7 @@
       </c>
     </row>
     <row r="87" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D87" s="104" t="s">
+      <c r="D87" s="97" t="s">
         <v>299</v>
       </c>
       <c r="E87" s="42" t="s">
@@ -23769,7 +23769,7 @@
       <c r="F87" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M87" s="104" t="s">
+      <c r="M87" s="97" t="s">
         <v>299</v>
       </c>
       <c r="N87" s="42" t="s">
@@ -23778,7 +23778,7 @@
       <c r="O87" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V87" s="104" t="s">
+      <c r="V87" s="97" t="s">
         <v>299</v>
       </c>
       <c r="W87" s="42" t="s">
@@ -23789,21 +23789,21 @@
       </c>
     </row>
     <row r="88" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D88" s="104"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="42" t="s">
         <v>281</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M88" s="104"/>
+      <c r="M88" s="97"/>
       <c r="N88" s="42" t="s">
         <v>281</v>
       </c>
       <c r="O88" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V88" s="104"/>
+      <c r="V88" s="97"/>
       <c r="W88" s="42" t="s">
         <v>281</v>
       </c>
@@ -23812,21 +23812,21 @@
       </c>
     </row>
     <row r="89" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D89" s="104"/>
+      <c r="D89" s="97"/>
       <c r="E89" s="42" t="s">
         <v>277</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M89" s="104"/>
+      <c r="M89" s="97"/>
       <c r="N89" s="42" t="s">
         <v>277</v>
       </c>
       <c r="O89" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V89" s="104"/>
+      <c r="V89" s="97"/>
       <c r="W89" s="42" t="s">
         <v>277</v>
       </c>
@@ -23835,21 +23835,21 @@
       </c>
     </row>
     <row r="90" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D90" s="104"/>
+      <c r="D90" s="97"/>
       <c r="E90" s="42" t="s">
         <v>283</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M90" s="104"/>
+      <c r="M90" s="97"/>
       <c r="N90" s="42" t="s">
         <v>283</v>
       </c>
       <c r="O90" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V90" s="104"/>
+      <c r="V90" s="97"/>
       <c r="W90" s="42" t="s">
         <v>283</v>
       </c>
@@ -23858,21 +23858,21 @@
       </c>
     </row>
     <row r="91" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D91" s="104"/>
+      <c r="D91" s="97"/>
       <c r="E91" s="42" t="s">
         <v>276</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M91" s="104"/>
+      <c r="M91" s="97"/>
       <c r="N91" s="42" t="s">
         <v>276</v>
       </c>
       <c r="O91" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V91" s="104"/>
+      <c r="V91" s="97"/>
       <c r="W91" s="42" t="s">
         <v>276</v>
       </c>
@@ -23881,21 +23881,21 @@
       </c>
     </row>
     <row r="92" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D92" s="104"/>
+      <c r="D92" s="97"/>
       <c r="E92" s="42" t="s">
         <v>278</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M92" s="104"/>
+      <c r="M92" s="97"/>
       <c r="N92" s="42" t="s">
         <v>278</v>
       </c>
       <c r="O92" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="V92" s="104"/>
+      <c r="V92" s="97"/>
       <c r="W92" s="42" t="s">
         <v>278</v>
       </c>
@@ -23991,7 +23991,7 @@
       </c>
     </row>
     <row r="96" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D96" s="104" t="s">
+      <c r="D96" s="97" t="s">
         <v>300</v>
       </c>
       <c r="E96" s="43" t="s">
@@ -24000,7 +24000,7 @@
       <c r="F96" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M96" s="104" t="s">
+      <c r="M96" s="97" t="s">
         <v>300</v>
       </c>
       <c r="N96" s="43" t="s">
@@ -24009,7 +24009,7 @@
       <c r="O96" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V96" s="104" t="s">
+      <c r="V96" s="97" t="s">
         <v>300</v>
       </c>
       <c r="W96" s="43" t="s">
@@ -24020,21 +24020,21 @@
       </c>
     </row>
     <row r="97" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D97" s="104"/>
+      <c r="D97" s="97"/>
       <c r="E97" s="43" t="s">
         <v>282</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M97" s="104"/>
+      <c r="M97" s="97"/>
       <c r="N97" s="43" t="s">
         <v>282</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V97" s="104"/>
+      <c r="V97" s="97"/>
       <c r="W97" s="43" t="s">
         <v>282</v>
       </c>
@@ -24043,21 +24043,21 @@
       </c>
     </row>
     <row r="98" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D98" s="104"/>
+      <c r="D98" s="97"/>
       <c r="E98" s="43" t="s">
         <v>302</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M98" s="104"/>
+      <c r="M98" s="97"/>
       <c r="N98" s="43" t="s">
         <v>302</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V98" s="104"/>
+      <c r="V98" s="97"/>
       <c r="W98" s="43" t="s">
         <v>302</v>
       </c>
@@ -24066,21 +24066,21 @@
       </c>
     </row>
     <row r="99" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D99" s="104"/>
+      <c r="D99" s="97"/>
       <c r="E99" s="43" t="s">
         <v>285</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M99" s="104"/>
+      <c r="M99" s="97"/>
       <c r="N99" s="43" t="s">
         <v>285</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V99" s="104"/>
+      <c r="V99" s="97"/>
       <c r="W99" s="43" t="s">
         <v>285</v>
       </c>
@@ -24089,21 +24089,21 @@
       </c>
     </row>
     <row r="100" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D100" s="104"/>
+      <c r="D100" s="97"/>
       <c r="E100" s="43" t="s">
         <v>276</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M100" s="104"/>
+      <c r="M100" s="97"/>
       <c r="N100" s="43" t="s">
         <v>276</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V100" s="104"/>
+      <c r="V100" s="97"/>
       <c r="W100" s="43" t="s">
         <v>276</v>
       </c>
@@ -24112,21 +24112,21 @@
       </c>
     </row>
     <row r="101" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D101" s="104"/>
+      <c r="D101" s="97"/>
       <c r="E101" s="43" t="s">
         <v>283</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M101" s="104"/>
+      <c r="M101" s="97"/>
       <c r="N101" s="43" t="s">
         <v>283</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V101" s="104"/>
+      <c r="V101" s="97"/>
       <c r="W101" s="43" t="s">
         <v>283</v>
       </c>
@@ -24135,7 +24135,7 @@
       </c>
     </row>
     <row r="102" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D102" s="104" t="s">
+      <c r="D102" s="97" t="s">
         <v>301</v>
       </c>
       <c r="E102" s="43" t="s">
@@ -24144,7 +24144,7 @@
       <c r="F102" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M102" s="104" t="s">
+      <c r="M102" s="97" t="s">
         <v>301</v>
       </c>
       <c r="N102" s="43" t="s">
@@ -24153,7 +24153,7 @@
       <c r="O102" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V102" s="104" t="s">
+      <c r="V102" s="97" t="s">
         <v>301</v>
       </c>
       <c r="W102" s="43" t="s">
@@ -24164,21 +24164,21 @@
       </c>
     </row>
     <row r="103" spans="4:24" x14ac:dyDescent="0.25">
-      <c r="D103" s="104"/>
+      <c r="D103" s="97"/>
       <c r="E103" s="43" t="s">
         <v>282</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M103" s="104"/>
+      <c r="M103" s="97"/>
       <c r="N103" s="43" t="s">
         <v>282</v>
       </c>
       <c r="O103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V103" s="104"/>
+      <c r="V103" s="97"/>
       <c r="W103" s="43" t="s">
         <v>282</v>
       </c>
@@ -24195,23 +24195,51 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="78">
-    <mergeCell ref="V73:V84"/>
-    <mergeCell ref="V85:V86"/>
-    <mergeCell ref="V87:V92"/>
-    <mergeCell ref="V96:V101"/>
-    <mergeCell ref="V102:V103"/>
-    <mergeCell ref="V71:V72"/>
-    <mergeCell ref="X20:Z20"/>
-    <mergeCell ref="AA20:AC20"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AC21"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="V24:V35"/>
-    <mergeCell ref="V36:V43"/>
-    <mergeCell ref="V44:V47"/>
-    <mergeCell ref="V52:V57"/>
-    <mergeCell ref="V58:V59"/>
-    <mergeCell ref="V69:V70"/>
+    <mergeCell ref="D96:D101"/>
+    <mergeCell ref="D52:D57"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="D73:D84"/>
+    <mergeCell ref="D36:D43"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="D87:D92"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:K16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M24:M35"/>
+    <mergeCell ref="M36:M43"/>
+    <mergeCell ref="M44:M47"/>
+    <mergeCell ref="M52:M57"/>
     <mergeCell ref="M102:M103"/>
     <mergeCell ref="V16:W16"/>
     <mergeCell ref="X16:AC16"/>
@@ -24228,51 +24256,23 @@
     <mergeCell ref="M85:M86"/>
     <mergeCell ref="M87:M92"/>
     <mergeCell ref="M96:M101"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M24:M35"/>
-    <mergeCell ref="M36:M43"/>
-    <mergeCell ref="M44:M47"/>
-    <mergeCell ref="M52:M57"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="D24:D35"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:K16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="D96:D101"/>
-    <mergeCell ref="D52:D57"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="D73:D84"/>
-    <mergeCell ref="D36:D43"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="D87:D92"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="V71:V72"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="AA20:AC20"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="V24:V35"/>
+    <mergeCell ref="V36:V43"/>
+    <mergeCell ref="V44:V47"/>
+    <mergeCell ref="V52:V57"/>
+    <mergeCell ref="V58:V59"/>
+    <mergeCell ref="V69:V70"/>
+    <mergeCell ref="V73:V84"/>
+    <mergeCell ref="V85:V86"/>
+    <mergeCell ref="V87:V92"/>
+    <mergeCell ref="V96:V101"/>
+    <mergeCell ref="V102:V103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -24308,10 +24308,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="112"/>
+      <c r="B1" s="113"/>
       <c r="C1" s="4" t="s">
         <v>13</v>
       </c>
@@ -34020,10 +34020,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="112"/>
+      <c r="B1" s="113"/>
       <c r="C1" s="4" t="s">
         <v>13</v>
       </c>
@@ -49022,7 +49022,7 @@
       <c r="AQ217" s="26"/>
       <c r="AR217" s="26"/>
     </row>
-    <row r="218" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20" t="s">
         <v>349</v>
       </c>
@@ -49135,7 +49135,7 @@
       <c r="AQ218" s="26"/>
       <c r="AR218" s="26"/>
     </row>
-    <row r="219" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A219" s="20" t="s">
         <v>347</v>
       </c>
@@ -49248,7 +49248,7 @@
       <c r="AQ219" s="26"/>
       <c r="AR219" s="26"/>
     </row>
-    <row r="220" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20" t="s">
         <v>345</v>
       </c>
@@ -49361,7 +49361,7 @@
       <c r="AQ220" s="26"/>
       <c r="AR220" s="26"/>
     </row>
-    <row r="221" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20" t="s">
         <v>343</v>
       </c>
@@ -49474,7 +49474,7 @@
       <c r="AQ221" s="26"/>
       <c r="AR221" s="26"/>
     </row>
-    <row r="222" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="s">
         <v>341</v>
       </c>
@@ -49587,7 +49587,7 @@
       <c r="AQ222" s="26"/>
       <c r="AR222" s="26"/>
     </row>
-    <row r="223" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20" t="s">
         <v>339</v>
       </c>
@@ -49700,7 +49700,7 @@
       <c r="AQ223" s="26"/>
       <c r="AR223" s="26"/>
     </row>
-    <row r="224" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="s">
         <v>337</v>
       </c>
@@ -49813,7 +49813,7 @@
       <c r="AQ224" s="26"/>
       <c r="AR224" s="26"/>
     </row>
-    <row r="225" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20" t="s">
         <v>335</v>
       </c>
@@ -49926,7 +49926,7 @@
       <c r="AQ225" s="26"/>
       <c r="AR225" s="26"/>
     </row>
-    <row r="226" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A226" s="91" t="s">
         <v>830</v>
       </c>
@@ -49984,7 +49984,7 @@
       <c r="AQ226" s="26"/>
       <c r="AR226" s="26"/>
     </row>
-    <row r="227" spans="1:44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A227" s="91" t="s">
         <v>831</v>
       </c>
@@ -50070,7 +50070,7 @@
       <c r="AQ227" s="26"/>
       <c r="AR227" s="26"/>
     </row>
-    <row r="228" spans="1:44" ht="30" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:44" ht="30" x14ac:dyDescent="0.25">
       <c r="A228" s="18" t="s">
         <v>178</v>
       </c>
